--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -108,28 +108,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"scope":"enemy","cd":3,"range":5,"pow":2,"flat":10,"elm":"ice","src":"int"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"scope":"self","cd":3,"pow":2,"flat":10,"src":"int"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>spell</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"scope":"enemy","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","sprite":{"img":"icons/1","scl":1,"deg":-45}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"scope":"self","type":"dot","value":2,"dur":3,"icon":"icons/0","tag":"bleed"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"scope":"self","type":"hot","value":5,"dur":5,"icon":"icons/16","tag":"heal"},
-{"scope":"self","type":"buff","effects":[{"stat":"str","a":1}],"dur":5,"icon":"icons/16","tag":"strong"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -184,6 +167,23 @@
   </si>
   <si>
     <t>icons:17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"scope":"self","type":"dot","value":2,"dur":3,"icon":"icons:0","tag":"bleed"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"scope":"self","type":"hot","value":5,"dur":5,"icon":"icons:16","tag":"heal"},
+{"scope":"self","type":"buff","effects":[{"stat":"str","a":1}],"dur":5,"icon":"icons:16","tag":"strong"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"scope":"enemy","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","sprite":{"img":"icons:1","scl":1,"deg":-45}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"scope":"enemy","cd":3,"range":5,"pow":2,"flat":10,"elm":"ice","src":"int","sprite":{"img":"icons:8","scl":1,"deg":-45}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -551,7 +551,7 @@
     <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.21875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="72.44140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="62.88671875" style="3" customWidth="1"/>
     <col min="6" max="6" width="39.44140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="95" style="3" customWidth="1"/>
     <col min="8" max="8" width="70" style="1" customWidth="1"/>
@@ -590,7 +590,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>14</v>
@@ -600,13 +600,13 @@
         <v>21</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="31.2">
@@ -614,16 +614,16 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="31.2">
@@ -631,19 +631,19 @@
         <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="31.2">
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
@@ -660,7 +660,7 @@
         <v>20</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="31.2">
@@ -668,19 +668,19 @@
         <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="31.2">
@@ -688,7 +688,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>7</v>

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
   <si>
     <t>strong</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -104,10 +104,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"scope":"enemy","cd":3,"range":2,"pow":1.5,"flat":0,"elm":"phy","src":"atk"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"scope":"self","cd":3,"pow":2,"flat":10,"src":"int"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -121,26 +117,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"scope":"self","stat":"pen","a":0.1},
-{"scope":"enemy","stat":"def","m":-0.1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"突刺",
-"des":"對目標造成{#fmt}點{#elm}傷害。{#eff}"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"火球術",
-"des":"對目標造成{#fmt}點{#elm}傷害。{#eff}"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"冰凍術",
-"des":"對目標造成{#fmt}點{#elm}傷害。{#eff}"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"lab":"強化",
 "des":"{#eff}"</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -179,11 +155,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"scope":"enemy","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","sprite":{"img":"icons:1","scl":1,"deg":-45}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"scope":"enemy","cd":3,"range":5,"pow":2,"flat":10,"elm":"ice","src":"int","sprite":{"img":"icons:8","scl":1,"deg":-45}</t>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"stage":"atk","scope":"self","type":"mod","key":"pen","a":0.1},
+{"stage":"atk","scope":"target","type":"mod","key":"def","m":-0.1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"突刺",
+"des":"對{#scope}造成{#pow}倍{#src}的{#elm}傷害。{#eff}"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"火球術",
+"des":"對{#scope}造成{#pow}倍{#src}的{#elm}傷害。{#eff}"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"冰凍術",
+"des":"對{#scope}造成{#pow}倍{#src}的{#elm}傷害。{#eff}"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"scope":"target","cd":3,"range":2,"pow":1.5,"flat":0,"elm":"phy","src":"atk"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"scope":"target","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","sprite":{"img":"icons:1","scl":1,"deg":-45}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"scope":"target","cd":3,"range":5,"pow":2,"flat":10,"elm":"ice","src":"int","sprite":{"img":"icons:8","scl":1,"deg":-45}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -544,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="10.21875" style="1" customWidth="1"/>
@@ -552,7 +556,7 @@
     <col min="3" max="3" width="10.109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.21875" style="1" customWidth="1"/>
     <col min="5" max="5" width="62.88671875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="39.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="84" style="1" customWidth="1"/>
     <col min="7" max="7" width="95" style="3" customWidth="1"/>
     <col min="8" max="8" width="70" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.77734375" style="1" customWidth="1"/>
@@ -590,23 +594,23 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="3" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="31.2">
@@ -614,16 +618,16 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="31.2">
@@ -631,19 +635,19 @@
         <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="31.2">
@@ -651,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
@@ -660,7 +664,7 @@
         <v>20</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="31.2">
@@ -668,19 +672,19 @@
         <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="31.2">
@@ -688,7 +692,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>7</v>
@@ -698,6 +702,11 @@
       </c>
       <c r="H7" s="3" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="E13" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>strong</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -100,29 +100,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"scope":"self","stat":"str","a":1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"scope":"self","cd":3,"pow":2,"flat":10,"src":"int"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>spell</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"回復術",
-"des":"回復{#fmt}點生命"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"強化",
-"des":"{#eff}"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -164,30 +146,53 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>"scope":"target","cd":3,"range":2,"pow":1.5,"flat":0,"elm":"phy","src":"atk"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"scope":"target","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","sprite":{"img":"icons:1","scl":1,"deg":-45}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"scope":"target","cd":3,"range":5,"pow":2,"flat":10,"elm":"ice","src":"int","sprite":{"img":"icons:8","scl":1,"deg":-45}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🗡️</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"scope":"self","type":"mod","key":"str","a":1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>"lab":"突刺",
-"des":"對{#scope}造成{#pow}倍{#src}的{#elm}傷害。{#eff}"</t>
+"des":"對{#scope}造成{#pow}倍{#src}的{#elm}傷害。"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"lab":"火球術",
-"des":"對{#scope}造成{#pow}倍{#src}的{#elm}傷害。{#eff}"</t>
+"des":"對{#scope}造成{#pow}倍{#src}的{#elm}傷害。"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"lab":"冰凍術",
-"des":"對{#scope}造成{#pow}倍{#src}的{#elm}傷害。{#eff}"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"scope":"target","cd":3,"range":2,"pow":1.5,"flat":0,"elm":"phy","src":"atk"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"scope":"target","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","sprite":{"img":"icons:1","scl":1,"deg":-45}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"scope":"target","cd":3,"range":5,"pow":2,"flat":10,"elm":"ice","src":"int","sprite":{"img":"icons:8","scl":1,"deg":-45}</t>
+"des":"對{#scope}造成{#pow}倍{#src}的{#elm}傷害。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"強化",
+"des":""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"回復術",
+"des":"回復{#pow}倍{#src}的生命"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"stage":"cast","scope":"self","type":"hot","a":5,"dur":5,"icon":"❤️","id":"heal"},
+{"stage":"cast","scope":"self","type":"buff","key":"str","a":1,"dur":100,"icon":"💪","id":"strong"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -556,7 +561,7 @@
     <col min="3" max="3" width="10.109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.21875" style="1" customWidth="1"/>
     <col min="5" max="5" width="62.88671875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="84" style="1" customWidth="1"/>
+    <col min="6" max="6" width="94.88671875" style="1" customWidth="1"/>
     <col min="7" max="7" width="95" style="3" customWidth="1"/>
     <col min="8" max="8" width="70" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.77734375" style="1" customWidth="1"/>
@@ -594,23 +599,23 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="31.2">
@@ -618,16 +623,16 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="31.2">
@@ -635,19 +640,19 @@
         <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="31.2">
@@ -655,16 +660,16 @@
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="31.2">
@@ -672,19 +677,22 @@
         <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="31.2">
@@ -692,7 +700,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>7</v>
@@ -706,7 +714,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="E13" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -50,10 +50,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>fireball</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"lunge",
 "fireball"</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -193,6 +189,10 @@
   <si>
     <t>{"stage":"cast","scope":"self","type":"hot","a":5,"dur":5,"icon":"❤️","id":"heal"},
 {"stage":"cast","scope":"self","type":"buff","key":"str","a":1,"dur":100,"icon":"💪","id":"strong"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fireball</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -582,13 +582,13 @@
         <v>4</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>5</v>
@@ -599,60 +599,60 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="31.2">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="31.2">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="31.2">
@@ -660,61 +660,61 @@
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="31.2">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="31.2">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="E13" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
   <si>
     <t>strong</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -72,10 +72,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>attack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ice</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -193,6 +189,22 @@
   </si>
   <si>
     <t>fireball</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heal</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -553,22 +565,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="10.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="62.88671875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="94.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="95" style="3" customWidth="1"/>
-    <col min="8" max="8" width="70" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.77734375" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="4" width="10.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="62.88671875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="94.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="95" style="3" customWidth="1"/>
+    <col min="9" max="9" width="70" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.77734375" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -579,142 +591,157 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="31.2">
+    <row r="2" spans="1:9" ht="31.2">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3" t="s">
-        <v>30</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="2"/>
       <c r="F2" s="3" t="s">
         <v>29</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="31.2">
+      <c r="A3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="31.2">
-      <c r="A3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" spans="1:9" ht="31.2">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="31.2">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="31.2">
+    <row r="5" spans="1:9" ht="31.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>38</v>
+      <c r="G5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="31.2">
+    <row r="6" spans="1:9" ht="31.2">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>19</v>
+      <c r="D6" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>39</v>
+        <v>26</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="31.2">
+    <row r="7" spans="1:9" ht="31.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="E13" s="3" t="s">
-        <v>28</v>
+    <row r="13" spans="1:9">
+      <c r="F13" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -183,28 +183,28 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>fireball</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>{"stage":"cast","scope":"self","type":"hot","a":5,"dur":5,"icon":"❤️","id":"heal"},
-{"stage":"cast","scope":"self","type":"buff","key":"str","a":1,"dur":100,"icon":"💪","id":"strong"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fireball</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tag</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>heal</t>
+{"stage":"cast","scope":"self","type":"buff","key":"str","a":1,"dur":100,"stack":1,"icon":"💪","id":"strong"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -573,7 +573,7 @@
     <col min="3" max="4" width="10.109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.21875" style="1" customWidth="1"/>
     <col min="6" max="6" width="62.88671875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="94.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="98.5546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="95" style="3" customWidth="1"/>
     <col min="9" max="9" width="70" style="1" customWidth="1"/>
     <col min="10" max="10" width="20.77734375" style="1" customWidth="1"/>
@@ -591,7 +591,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -617,10 +617,10 @@
         <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="3" t="s">
@@ -638,7 +638,7 @@
     </row>
     <row r="3" spans="1:9" ht="31.2">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>20</v>
@@ -647,7 +647,7 @@
         <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>30</v>
@@ -667,7 +667,7 @@
         <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
@@ -696,7 +696,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="31.2">
+    <row r="6" spans="1:9" ht="46.8">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -707,13 +707,13 @@
         <v>7</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>26</v>

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -4,23 +4,24 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868"/>
+    <workbookView xWindow="744" yWindow="1188" windowWidth="19200" windowHeight="6456" activeTab="7"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="general" sheetId="1" r:id="rId1"/>
+    <sheet name="sword" sheetId="2" r:id="rId2"/>
+    <sheet name="archery" sheetId="3" r:id="rId3"/>
+    <sheet name="fire" sheetId="4" r:id="rId4"/>
+    <sheet name="ice" sheetId="5" r:id="rId5"/>
+    <sheet name="poison" sheetId="6" r:id="rId6"/>
+    <sheet name="support" sheetId="7" r:id="rId7"/>
+    <sheet name="enhancement" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
-  <si>
-    <t>strong</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="125">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -42,7 +43,501 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>lunge</t>
+    <t>effects</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meta</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🧤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"偷竊",
+"des":"從 NPC 或怪物身上獲取財物。成功率視敏捷而定。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🗝️</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"開鎖",
+"des":"破解寶箱或門鎖。解鎖更高難度的鎖具。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"剝皮",
+"des":"從野獸屍體獲取皮革。增加素材掉落率。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🔪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>👤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>💰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"潛行",
+"des":"進入半透明狀態，大幅降低敵方偵測範圍。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"討價還價",
+"des":"交易時獲得更好價格。商店售價 -15%，回收價 +15%。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🗡️</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>📍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🌪️</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"斬擊",
+"des":"基本橫劈，對前方弧形範圍造成 115% 傷害。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"刺擊",
+"des":"直線突刺。無視目標 20% 物理防禦。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"旋風斬",
+"des":"旋轉劍身，對周圍全體造成多段傷害。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🎯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"狙擊",
+"des":"瞄準敵人的弱點射擊，造成 250% 的傷害。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🔥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"火球術",
+"des":"投擲火球。造成基礎火屬性爆炸傷害。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"火牆術",
+"des":"召喚火焰地帶。對經過者施加持續灼燒。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"燃燒術",
+"des":"引爆目標身上的灼燒狀態，造成瞬間大傷害。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"流星雨",
+"des":"大範圍隕石轟炸，摧毀範圍內一切。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🧱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🌋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>☄️</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>❄️</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🧊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🥶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🌨️</t>
+  </si>
+  <si>
+    <t>"lab":"冰箭術",
+"des":"單體冰錐。造成傷害並減速 30%。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"冰牆術",
+"des":"召喚可抵擋飛行道具的冰塊物理障礙物。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"冰封術",
+"des":"將減速狀態轉為凍結，使敵方完全無法行動 3 秒。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"暴風雪",
+"des":"大範圍持續性傷害，並有 10% 機率直接凍結敵人。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"毒箭術",
+"des":"遠程發射毒針，使目標進入每秒扣血的中毒狀態。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🐍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🌫️</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"毒霧術",
+"des":"在指定區域散佈致命毒氣。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🍄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"毒素引爆",
+"des":"使受毒者爆炸，將毒素噴濺至周圍目標。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"治療",
+"des":"恢復目標生命值。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"解毒",
+"des":"清除體內毒素。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"淨化",
+"des":"清除體內毒素，移除所有負面狀態。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"聖光",
+"des":"移除 1 個負面狀態。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>✨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>💖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>☀️</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🧪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>💪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>👟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🧠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"敏捷增強",
+"des":"增加敏捷，可提升閃避。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"智力增強",
+"des":"增加智力，可提升法術效果。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"力量增強",
+"des":"增加力量，可提升近戰傷害。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>us</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Stealing",
+"des":"從 NPC 或怪物身上獲取財物。成功率視敏捷而定。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Lockpicking",
+"des":"破解寶箱或門鎖。解鎖更高難度的鎖具。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Skinning",
+"des":"從野獸屍體獲取皮革。增加素材掉落率。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Stealth",
+"des":"進入半透明狀態，大幅降低敵方偵測範圍。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Barter",
+"des":"交易時獲得更好價格。商店售價 -15%，回收價 +15%。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>us</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Slash",
+"des":"基本橫劈，對前方弧形範圍造成 115% 傷害。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Thrust",
+"des":"直線突刺。無視目標 20% 物理防禦。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Whirlwind",
+"des":"旋轉劍身，對周圍全體造成多段傷害。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Snipe",
+"des":"瞄準敵人的弱點射擊，造成 250% 的傷害。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Fireball",
+"des":"投擲火球。造成基礎火屬性爆炸傷害。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Fire Wall",
+"des":"召喚火焰地帶。對經過者施加持續灼燒。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Combustion",
+"des":"引爆目標身上的灼燒狀態，造成瞬間大傷害。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Meteor Shower",
+"des":"大範圍隕石轟炸，摧毀範圍內一切。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Ice Bolt",
+"des":"單體冰錐。造成傷害並減速 30%。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Ice Wall",
+"des":"召喚可抵擋飛行道具的冰塊物理障礙物。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Deep Freeze",
+"des":"將減速狀態轉為凍結，使敵方完全無法行動 3 秒。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Blizzard",
+"des":"大範圍持續性傷害，並有 10% 機率直接凍結敵人。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Heal",
+"des":"恢復目標生命值。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Cure",
+"des":"清除體內毒素。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Holy Light",
+"des":"移除 1 個負面狀態。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Purify",
+"des":"清除體內毒素，移除所有負面狀態。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Strength Boost",
+"des":"增加力量，可提升近戰傷害。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Agility Boost",
+"des":"增加敏捷，可提升閃避。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Intelligence Boost",
+"des":"增加智力，可提升法術效果。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stealing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lockpicking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skinning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stealth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>barter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thrust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>whirlwind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snipe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fireball</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>firewall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meteorshower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icebolt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icewall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deepfreeze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blizzard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poisondart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poisonmist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>venomburst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>holylight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>purify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strboost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agiboost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intboost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>combustion</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -50,161 +545,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"lunge",
-"fireball"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>passive</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>test1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"測試1",
-"des":"測試1"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"cd":3,"range":2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ice</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>heal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>procs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>effects</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>meta</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"scope":"self","cd":3,"pow":2,"flat":10,"src":"int"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>spell</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:17</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"scope":"self","type":"dot","value":2,"dur":3,"icon":"icons:0","tag":"bleed"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"scope":"self","type":"hot","value":5,"dur":5,"icon":"icons:16","tag":"heal"},
-{"scope":"self","type":"buff","effects":[{"stat":"str","a":1}],"dur":5,"icon":"icons:16","tag":"strong"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"stage":"atk","scope":"self","type":"mod","key":"pen","a":0.1},
-{"stage":"atk","scope":"target","type":"mod","key":"def","m":-0.1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"scope":"target","cd":3,"range":2,"pow":1.5,"flat":0,"elm":"phy","src":"atk"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"scope":"target","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","sprite":{"img":"icons:1","scl":1,"deg":-45}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"scope":"target","cd":3,"range":5,"pow":2,"flat":10,"elm":"ice","src":"int","sprite":{"img":"icons:8","scl":1,"deg":-45}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>🗡️</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"scope":"self","type":"mod","key":"str","a":1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"突刺",
-"des":"對{#scope}造成{#pow}倍{#src}的{#elm}傷害。"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"火球術",
-"des":"對{#scope}造成{#pow}倍{#src}的{#elm}傷害。"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"冰凍術",
-"des":"對{#scope}造成{#pow}倍{#src}的{#elm}傷害。"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"強化",
-"des":""</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"回復術",
-"des":"回復{#pow}倍{#src}的生命"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fireball</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tag</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>heal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"stage":"cast","scope":"self","type":"hot","a":5,"dur":5,"icon":"❤️","id":"heal"},
-{"stage":"cast","scope":"self","type":"buff","key":"str","a":1,"dur":100,"stack":1,"icon":"💪","id":"strong"}</t>
+    <t>"slash","thrust"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"fireball",
+"firewall"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"combustion"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"icebolt",
+"icewall"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"deepfreeze"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"poisondart",
+"poisonmist"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"cure",
+"holylight"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -568,180 +937,141 @@
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="10.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
     <col min="3" max="4" width="10.109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="62.88671875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="98.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="95" style="3" customWidth="1"/>
-    <col min="9" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="10" width="20.77734375" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="14.109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="64.109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="67.21875" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="31.2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="31.2">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>30</v>
+        <v>117</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.2">
       <c r="A4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="H4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="I4" s="3" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="31.2">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>33</v>
+        <v>117</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="46.8">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="31.2">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="I6" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="31.2">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="H7" s="3"/>
     </row>
     <row r="13" spans="1:9">
       <c r="F13" s="3" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -753,9 +1083,102 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
-  <sheetData/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" style="1" customWidth="1"/>
+    <col min="2" max="4" width="8.88671875" style="1"/>
+    <col min="5" max="5" width="15.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="1" customWidth="1"/>
+    <col min="8" max="9" width="66.33203125" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="31.2">
+      <c r="A2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="31.2">
+      <c r="A3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="31.2">
+      <c r="A4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
@@ -764,11 +1187,737 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
-  <sheetData/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" style="1" customWidth="1"/>
+    <col min="2" max="5" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="14.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="1" customWidth="1"/>
+    <col min="8" max="9" width="66.33203125" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="31.2">
+      <c r="A2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="18.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
+    <col min="8" max="9" width="70" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="31.2">
+      <c r="A2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="31.2">
+      <c r="A3" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="31.2">
+      <c r="A4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="31.2">
+      <c r="A5" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="F13" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="18.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
+    <col min="8" max="9" width="70" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="31.2">
+      <c r="A2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="31.2">
+      <c r="A3" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="31.2">
+      <c r="A4" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="31.2">
+      <c r="A5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="F13" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="18.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="61" style="1" customWidth="1"/>
+    <col min="9" max="9" width="70" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="31.2">
+      <c r="A2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="31.2">
+      <c r="A3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="31.2">
+      <c r="A4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="16.2">
+      <c r="B5"/>
+      <c r="F5" s="1"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="F13" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="18.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="48.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="70" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="31.2">
+      <c r="A2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="31.2">
+      <c r="A3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="31.2">
+      <c r="A4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="46.8">
+      <c r="A5" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="F13" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="23.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
+    <col min="8" max="9" width="46" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="31.2">
+      <c r="A2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="31.2">
+      <c r="A3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="31.2">
+      <c r="A4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="H4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="F12" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="744" yWindow="1188" windowWidth="19200" windowHeight="6456" activeTab="7"/>
+    <workbookView xWindow="744" yWindow="1188" windowWidth="19200" windowHeight="6456" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="130">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -574,6 +574,26 @@
   <si>
     <t>"cure",
 "holylight"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"scope":"target","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","sprite":{"img":"icons:1","scl":1,"deg":-45}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>active</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"scope":"target","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","sprite":{"img":"🔥","size":25,"deg":-90}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1268,7 +1288,7 @@
     <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
     <col min="3" max="4" width="10.109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="18.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="59.6640625" style="3" customWidth="1"/>
     <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
     <col min="8" max="9" width="70" style="1" customWidth="1"/>
     <col min="10" max="16384" width="8.88671875" style="1"/>
@@ -1311,9 +1331,15 @@
         <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="E2" s="2"/>
+      <c r="F2" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
         <v>29</v>
@@ -1330,7 +1356,10 @@
         <v>33</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>125</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>30</v>
@@ -1764,7 +1793,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="46.8">
+    <row r="5" spans="1:9" ht="31.2">
       <c r="A5" s="1" t="s">
         <v>112</v>
       </c>
@@ -1919,5 +1948,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="744" yWindow="1188" windowWidth="19200" windowHeight="6456" activeTab="3"/>
+    <workbookView xWindow="744" yWindow="1188" windowWidth="19200" windowHeight="6456"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -433,18 +433,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>stealing</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lockpicking</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skinning</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>stealth</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -594,6 +582,18 @@
   </si>
   <si>
     <t>"scope":"target","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","sprite":{"img":"🔥","size":25,"deg":-90}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>steal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lockpick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skin</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -999,13 +999,13 @@
     </row>
     <row r="2" spans="1:9" ht="31.2">
       <c r="A2" s="1" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E2" s="2"/>
       <c r="G2" s="3"/>
@@ -1018,13 +1018,13 @@
     </row>
     <row r="3" spans="1:9" ht="31.2">
       <c r="A3" s="1" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>12</v>
@@ -1035,13 +1035,13 @@
     </row>
     <row r="4" spans="1:9" ht="31.2">
       <c r="A4" s="1" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E4" s="3"/>
       <c r="H4" s="3" t="s">
@@ -1053,13 +1053,13 @@
     </row>
     <row r="5" spans="1:9" ht="31.2">
       <c r="A5" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>17</v>
@@ -1070,13 +1070,13 @@
     </row>
     <row r="6" spans="1:9" ht="31.2">
       <c r="A6" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
@@ -1146,13 +1146,13 @@
     </row>
     <row r="2" spans="1:9" ht="31.2">
       <c r="A2" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
@@ -1163,13 +1163,13 @@
     </row>
     <row r="3" spans="1:9" ht="31.2">
       <c r="A3" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>24</v>
@@ -1180,16 +1180,16 @@
     </row>
     <row r="4" spans="1:9" ht="31.2">
       <c r="A4" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>25</v>
@@ -1249,13 +1249,13 @@
     </row>
     <row r="2" spans="1:9" ht="31.2">
       <c r="A2" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>27</v>
@@ -1325,20 +1325,20 @@
     </row>
     <row r="2" spans="1:9" ht="31.2">
       <c r="A2" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
@@ -1350,16 +1350,16 @@
     </row>
     <row r="3" spans="1:9" ht="31.2">
       <c r="A3" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>30</v>
@@ -1370,16 +1370,16 @@
     </row>
     <row r="4" spans="1:9" ht="31.2">
       <c r="A4" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -1390,16 +1390,16 @@
     </row>
     <row r="5" spans="1:9" ht="31.2">
       <c r="A5" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -1474,13 +1474,13 @@
     </row>
     <row r="2" spans="1:9" ht="31.2">
       <c r="A2" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E2" s="2"/>
       <c r="G2" s="3"/>
@@ -1493,13 +1493,13 @@
     </row>
     <row r="3" spans="1:9" ht="31.2">
       <c r="A3" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>41</v>
@@ -1510,16 +1510,16 @@
     </row>
     <row r="4" spans="1:9" ht="31.2">
       <c r="A4" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>42</v>
@@ -1530,16 +1530,16 @@
     </row>
     <row r="5" spans="1:9" ht="31.2">
       <c r="A5" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s">
         <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>43</v>
@@ -1615,13 +1615,13 @@
     </row>
     <row r="2" spans="1:9" ht="31.2">
       <c r="A2" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E2" s="2"/>
       <c r="G2" s="3"/>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="3" spans="1:9" ht="31.2">
       <c r="A3" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>47</v>
@@ -1651,16 +1651,16 @@
     </row>
     <row r="4" spans="1:9" ht="31.2">
       <c r="A4" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>49</v>
@@ -1743,13 +1743,13 @@
     </row>
     <row r="2" spans="1:9" ht="31.2">
       <c r="A2" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
@@ -1761,13 +1761,13 @@
     </row>
     <row r="3" spans="1:9" ht="31.2">
       <c r="A3" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>51</v>
@@ -1778,13 +1778,13 @@
     </row>
     <row r="4" spans="1:9" ht="31.2">
       <c r="A4" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>53</v>
@@ -1795,16 +1795,16 @@
     </row>
     <row r="5" spans="1:9" ht="31.2">
       <c r="A5" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>54</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>52</v>
@@ -1879,13 +1879,13 @@
     </row>
     <row r="2" spans="1:9" ht="31.2">
       <c r="A2" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E2" s="2"/>
       <c r="G2" s="3"/>
@@ -1898,13 +1898,13 @@
     </row>
     <row r="3" spans="1:9" ht="31.2">
       <c r="A3" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>61</v>
@@ -1915,13 +1915,13 @@
     </row>
     <row r="4" spans="1:9" ht="31.2">
       <c r="A4" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E4" s="3"/>
       <c r="H4" s="3" t="s">

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="744" yWindow="1188" windowWidth="19200" windowHeight="6456"/>
+    <workbookView xWindow="750" yWindow="1185" windowWidth="19200" windowHeight="6450"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="131">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -594,6 +594,10 @@
   </si>
   <si>
     <t>skin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lockpick</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -955,17 +959,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="64.109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="67.21875" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="12.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.25" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="64.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="67.25" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -997,7 +1001,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.2">
+    <row r="2" spans="1:9" ht="31.5">
       <c r="A2" s="1" t="s">
         <v>127</v>
       </c>
@@ -1016,7 +1020,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.2">
+    <row r="3" spans="1:9" ht="31.5">
       <c r="A3" s="1" t="s">
         <v>128</v>
       </c>
@@ -1026,6 +1030,9 @@
       <c r="C3" s="1" t="s">
         <v>114</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="H3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1033,7 +1040,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="31.2">
+    <row r="4" spans="1:9" ht="31.5">
       <c r="A4" s="1" t="s">
         <v>129</v>
       </c>
@@ -1051,7 +1058,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="31.2">
+    <row r="5" spans="1:9" ht="31.5">
       <c r="A5" s="1" t="s">
         <v>90</v>
       </c>
@@ -1068,7 +1075,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="31.2">
+    <row r="6" spans="1:9" ht="31.5">
       <c r="A6" s="1" t="s">
         <v>91</v>
       </c>
@@ -1104,15 +1111,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="1" customWidth="1"/>
-    <col min="2" max="4" width="8.88671875" style="1"/>
-    <col min="5" max="5" width="15.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.77734375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="1" customWidth="1"/>
-    <col min="8" max="9" width="66.33203125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
+    <col min="2" max="4" width="8.875" style="1"/>
+    <col min="5" max="5" width="15.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" style="1" customWidth="1"/>
+    <col min="8" max="9" width="66.375" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1144,7 +1151,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.2">
+    <row r="2" spans="1:9" ht="31.5">
       <c r="A2" s="1" t="s">
         <v>92</v>
       </c>
@@ -1161,7 +1168,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.2">
+    <row r="3" spans="1:9" ht="31.5">
       <c r="A3" s="1" t="s">
         <v>93</v>
       </c>
@@ -1178,7 +1185,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="31.2">
+    <row r="4" spans="1:9" ht="31.5">
       <c r="A4" s="1" t="s">
         <v>94</v>
       </c>
@@ -1208,14 +1215,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="1" customWidth="1"/>
-    <col min="2" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="6" width="14.77734375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="1" customWidth="1"/>
-    <col min="8" max="9" width="66.33203125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
+    <col min="2" max="5" width="8.875" style="1"/>
+    <col min="6" max="6" width="14.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" style="1" customWidth="1"/>
+    <col min="8" max="9" width="66.375" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1247,7 +1254,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.2">
+    <row r="2" spans="1:9" ht="31.5">
       <c r="A2" s="1" t="s">
         <v>95</v>
       </c>
@@ -1282,16 +1289,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="59.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.25" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="59.625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
     <col min="8" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="10" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1323,7 +1330,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.2">
+    <row r="2" spans="1:9" ht="31.5">
       <c r="A2" s="1" t="s">
         <v>96</v>
       </c>
@@ -1348,7 +1355,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.2">
+    <row r="3" spans="1:9" ht="31.5">
       <c r="A3" s="1" t="s">
         <v>97</v>
       </c>
@@ -1368,7 +1375,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="31.2">
+    <row r="4" spans="1:9" ht="31.5">
       <c r="A4" s="1" t="s">
         <v>113</v>
       </c>
@@ -1388,7 +1395,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="31.2">
+    <row r="5" spans="1:9" ht="31.5">
       <c r="A5" s="1" t="s">
         <v>98</v>
       </c>
@@ -1431,16 +1438,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.25" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
     <col min="8" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="10" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1472,7 +1479,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.2">
+    <row r="2" spans="1:9" ht="31.5">
       <c r="A2" s="1" t="s">
         <v>99</v>
       </c>
@@ -1491,7 +1498,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.2">
+    <row r="3" spans="1:9" ht="31.5">
       <c r="A3" s="1" t="s">
         <v>100</v>
       </c>
@@ -1508,7 +1515,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="31.2">
+    <row r="4" spans="1:9" ht="31.5">
       <c r="A4" s="1" t="s">
         <v>101</v>
       </c>
@@ -1528,7 +1535,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="31.2">
+    <row r="5" spans="1:9" ht="31.5">
       <c r="A5" s="1" t="s">
         <v>102</v>
       </c>
@@ -1571,17 +1578,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.25" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
     <col min="8" max="8" width="61" style="1" customWidth="1"/>
     <col min="9" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="10" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1613,7 +1620,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.2">
+    <row r="2" spans="1:9" ht="31.5">
       <c r="A2" s="1" t="s">
         <v>103</v>
       </c>
@@ -1632,7 +1639,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.2">
+    <row r="3" spans="1:9" ht="31.5">
       <c r="A3" s="1" t="s">
         <v>104</v>
       </c>
@@ -1649,7 +1656,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="31.2">
+    <row r="4" spans="1:9" ht="31.5">
       <c r="A4" s="1" t="s">
         <v>105</v>
       </c>
@@ -1669,7 +1676,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16.2">
+    <row r="5" spans="1:9" ht="16.5">
       <c r="B5"/>
       <c r="F5" s="1"/>
       <c r="H5" s="3"/>
@@ -1699,17 +1706,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.25" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="14" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="48.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="48.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="10" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1741,7 +1748,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.2">
+    <row r="2" spans="1:9" ht="31.5">
       <c r="A2" s="1" t="s">
         <v>106</v>
       </c>
@@ -1759,7 +1766,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.2">
+    <row r="3" spans="1:9" ht="31.5">
       <c r="A3" s="1" t="s">
         <v>107</v>
       </c>
@@ -1776,7 +1783,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="31.2">
+    <row r="4" spans="1:9" ht="31.5">
       <c r="A4" s="1" t="s">
         <v>108</v>
       </c>
@@ -1793,7 +1800,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="31.2">
+    <row r="5" spans="1:9" ht="31.5">
       <c r="A5" s="1" t="s">
         <v>109</v>
       </c>
@@ -1836,16 +1843,16 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="23.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.25" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
     <col min="8" max="9" width="46" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="10" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1877,7 +1884,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.2">
+    <row r="2" spans="1:9" ht="31.5">
       <c r="A2" s="1" t="s">
         <v>110</v>
       </c>
@@ -1896,7 +1903,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.2">
+    <row r="3" spans="1:9" ht="31.5">
       <c r="A3" s="1" t="s">
         <v>111</v>
       </c>
@@ -1913,7 +1920,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="31.2">
+    <row r="4" spans="1:9" ht="31.5">
       <c r="A4" s="1" t="s">
         <v>112</v>
       </c>

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="133">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -598,6 +598,14 @@
   </si>
   <si>
     <t>lockpick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>steal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skin</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1011,6 +1019,9 @@
       <c r="C2" s="1" t="s">
         <v>114</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="E2" s="2"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
@@ -1049,6 +1060,9 @@
       </c>
       <c r="C4" s="1" t="s">
         <v>114</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="E4" s="3"/>
       <c r="H4" s="3" t="s">

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="132">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -77,15 +77,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"lab":"剝皮",
-"des":"從野獸屍體獲取皮革。增加素材掉落率。"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>🔪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>👤</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -319,11 +310,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"lab":"Skinning",
-"des":"從野獸屍體獲取皮革。增加素材掉落率。"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"lab":"Stealth",
 "des":"進入半透明狀態，大幅降低敵方偵測範圍。"</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -593,10 +579,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>skin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>lockpick</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -605,7 +587,21 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>skin</t>
+    <t>butcher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🔪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Butcher",
+"des":"分解動物屍體，取得肉類、皮毛與骨頭...等可用素材。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"解剖",
+"des":"分解動物屍體，取得肉類、皮毛與骨頭...等可用素材。"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1006,21 +1002,21 @@
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="31.5">
       <c r="A2" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E2" s="2"/>
       <c r="G2" s="3"/>
@@ -1028,83 +1024,83 @@
         <v>10</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="31.5">
       <c r="A3" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5">
       <c r="A4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="31.5">
       <c r="A5" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="31.5">
       <c r="A6" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1141,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1162,61 +1158,61 @@
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="31.5">
       <c r="A2" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="31.5">
       <c r="A3" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5">
       <c r="A4" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1244,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1265,24 +1261,24 @@
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="31.5">
       <c r="A2" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1341,92 +1337,92 @@
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="31.5">
       <c r="A2" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="31.5">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5">
       <c r="A4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="31.5">
       <c r="A5" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="H5" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1490,83 +1486,83 @@
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="31.5">
       <c r="A2" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E2" s="2"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="31.5">
       <c r="A3" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5">
       <c r="A4" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="31.5">
       <c r="A5" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1631,63 +1627,63 @@
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="31.5">
       <c r="A2" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E2" s="2"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="31.5">
       <c r="A3" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5">
       <c r="A4" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.5">
@@ -1759,79 +1755,79 @@
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="31.5">
       <c r="A2" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="31.5">
       <c r="A3" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5">
       <c r="A4" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="31.5">
       <c r="A5" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1895,61 +1891,61 @@
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="31.5">
       <c r="A2" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E2" s="2"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="31.5">
       <c r="A3" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="I3" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5">
       <c r="A4" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:9">

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -29,7 +29,7 @@
     <t>icon</t>
   </si>
   <si>
-    <t>type</t>
+    <t>mode</t>
   </si>
   <si>
     <t>tag</t>

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="150">
   <si>
     <t>id</t>
   </si>
@@ -174,6 +174,51 @@
 "des":"旋轉劍身，對周圍全體造成多段傷害。"</t>
   </si>
   <si>
+    <t>swordmastery</t>
+  </si>
+  <si>
+    <t>⚔️</t>
+  </si>
+  <si>
+    <t>passive</t>
+  </si>
+  <si>
+    <t>buff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.1,"reqClass":"sword"},
+{"type":"mod","key":"atk","m":0.1,"reqClass":"sword"}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab":"劍術專家",
+"des":"精通劍術。裝備劍類武器時，命中+10%、攻擊力+10%。"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab":"Sword Expertise",
+"des":"Mastery of swordsmanship. +10% accuracy and +10% attack power while wielding a sword."</t>
+  </si>
+  <si>
+    <t>swordmaster</t>
+  </si>
+  <si>
+    <t>👑</t>
+  </si>
+  <si>
+    <t>"swordmastery"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.15,"reqClass":"sword"},
+{"type":"mod","key":"atk","m":0.15,"reqClass":"sword"}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab":"劍術大師",
+"des":"劍術造詣爐火純青。裝備劍類武器時，命中與攻擊力再進一步大幅提升。"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab":"Sword Mastery",
+"des":"Peak swordsmanship. Further boosts accuracy and attack power while wielding a sword."</t>
+  </si>
+  <si>
     <t>snipe</t>
   </si>
   <si>
@@ -188,6 +233,45 @@
 "des":"瞄準敵人的弱點射擊，造成 250% 的傷害。"</t>
   </si>
   <si>
+    <t>archeryexpert</t>
+  </si>
+  <si>
+    <t>🏹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.1,"reqClass":"bow"},
+{"type":"mod","key":"atk","m":0.1,"reqClass":"bow"}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab":"弓箭專家",
+"des":"精通弓術。裝備弓類武器時，命中+10%、攻擊力+10%。"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab":"Archery Expertise",
+"des":"Mastery of archery. +10% accuracy and +10% attack power while wielding a bow."</t>
+  </si>
+  <si>
+    <t>archerymaster</t>
+  </si>
+  <si>
+    <t>🎖️</t>
+  </si>
+  <si>
+    <t>"archeryexpert"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.15,"reqClass":"bow"},
+{"type":"mod","key":"atk","m":0.15,"reqClass":"bow"}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab":"弓箭大師",
+"des":"弓術造詣爐火純青。裝備弓類武器時，命中與攻擊力再進一步大幅提升。"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab":"Archery Mastery",
+"des":"Peak archery. Further boosts accuracy and attack power while wielding a bow."</t>
+  </si>
+  <si>
     <t>fireball</t>
   </si>
   <si>
@@ -418,9 +502,6 @@
   </si>
   <si>
     <t>💪</t>
-  </si>
-  <si>
-    <t>buff</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"力量增強",
@@ -967,7 +1048,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
@@ -1021,6 +1102,9 @@
       <c r="D2" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
       <c r="H2" s="2" t="s">
         <v>34</v>
       </c>
@@ -1069,6 +1153,58 @@
       </c>
       <c r="I4" s="2" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1121,10 +1257,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
@@ -1132,20 +1268,67 @@
       <c r="D2" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
       <c r="H2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="3" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1199,10 +1382,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
@@ -1212,22 +1395,22 @@
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
@@ -1236,21 +1419,21 @@
         <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -1259,21 +1442,21 @@
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
@@ -1282,13 +1465,13 @@
         <v>33</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -1357,10 +1540,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
@@ -1371,18 +1554,18 @@
       <c r="E2" s="1"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
@@ -1391,18 +1574,18 @@
         <v>33</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -1411,21 +1594,21 @@
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
@@ -1434,13 +1617,13 @@
         <v>33</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -1510,10 +1693,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
@@ -1524,18 +1707,18 @@
       <c r="E2" s="1"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
@@ -1544,18 +1727,18 @@
         <v>33</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -1564,13 +1747,13 @@
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
@@ -1646,86 +1829,86 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -1794,65 +1977,65 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="E2" s="1"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="E4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:9" x14ac:dyDescent="0.25">

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="151">
   <si>
     <t>id</t>
   </si>
@@ -166,6 +166,9 @@
     <t>"slash","thrust"</t>
   </si>
   <si>
+    <t>"scope":"group","radius":1</t>
+  </si>
+  <si>
     <t xml:space="preserve">"lab":"旋風斬",
 "des":"旋轉劍身，對周圍全體造成多段傷害。"</t>
   </si>
@@ -278,7 +281,7 @@
     <t>🔥</t>
   </si>
   <si>
-    <t>"scope":"target","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","sprite":{"img":"🔥","size":25,"deg":-90},"cast":"spell"</t>
+    <t>"scope":"single","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","sprite":{"img":"🔥","size":25,"deg":-90},"cast":"spell"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"火球術",
@@ -295,7 +298,7 @@
     <t>🧱</t>
   </si>
   <si>
-    <t>"scope":"target","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","sprite":{"img":"icons:1","scl":1,"deg":-45},"cast":"spell"</t>
+    <t>"scope":"single","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","sprite":{"img":"icons:1","scl":1,"deg":-45},"cast":"spell"</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"火牆術",
@@ -1148,63 +1151,66 @@
       <c r="E4" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="H4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1257,10 +1263,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
@@ -1272,62 +1278,62 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1382,10 +1388,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
@@ -1395,22 +1401,22 @@
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
@@ -1419,21 +1425,21 @@
         <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -1442,21 +1448,21 @@
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
@@ -1465,13 +1471,13 @@
         <v>33</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -1540,10 +1546,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
@@ -1554,18 +1560,18 @@
       <c r="E2" s="1"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
@@ -1574,18 +1580,18 @@
         <v>33</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -1594,21 +1600,21 @@
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
@@ -1617,13 +1623,13 @@
         <v>33</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -1693,10 +1699,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
@@ -1707,18 +1713,18 @@
       <c r="E2" s="1"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
@@ -1727,18 +1733,18 @@
         <v>33</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -1747,13 +1753,13 @@
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
@@ -1829,86 +1835,86 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -1977,65 +1983,65 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E2" s="1"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="7:9" x14ac:dyDescent="0.25">

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="157">
   <si>
     <t>id</t>
   </si>
@@ -135,6 +135,9 @@
     <t>atk</t>
   </si>
   <si>
+    <t>"cd":1</t>
+  </si>
+  <si>
     <t xml:space="preserve">"lab":"斬擊",
 "des":"基本橫劈，對前方弧形範圍造成 115% 傷害。"</t>
   </si>
@@ -166,7 +169,7 @@
     <t>"slash","thrust"</t>
   </si>
   <si>
-    <t>"scope":"group","radius":1</t>
+    <t>"cd":3,"scope":"group","radius":1</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"旋風斬",
@@ -228,6 +231,9 @@
     <t>🎯</t>
   </si>
   <si>
+    <t>"cd":3</t>
+  </si>
+  <si>
     <t xml:space="preserve">"lab":"狙擊",
 "des":"瞄準敵人的弱點射擊，造成 250% 的傷害。"</t>
   </si>
@@ -319,6 +325,9 @@
 "firewall"</t>
   </si>
   <si>
+    <t>"cd":4</t>
+  </si>
+  <si>
     <t xml:space="preserve">"lab":"燃燒術",
 "des":"引爆目標身上的灼燒狀態，造成瞬間大傷害。"</t>
   </si>
@@ -336,6 +345,9 @@
     <t>"combustion"</t>
   </si>
   <si>
+    <t>"cd":6</t>
+  </si>
+  <si>
     <t xml:space="preserve">"lab":"流星雨",
 "des":"大範圍隕石轟炸，摧毀範圍內一切。"</t>
   </si>
@@ -447,6 +459,9 @@
     <t>💖</t>
   </si>
   <si>
+    <t>"cd":2</t>
+  </si>
+  <si>
     <t xml:space="preserve">"lab":"治療",
 "des":"恢復目標生命值。"</t>
   </si>
@@ -491,6 +506,9 @@
   <si>
     <t xml:space="preserve">"cure",
 "holylight"</t>
+  </si>
+  <si>
+    <t>"cd":5</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"淨化",
@@ -1106,21 +1124,23 @@
         <v>33</v>
       </c>
       <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="G2" s="1"/>
       <c r="H2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
@@ -1128,19 +1148,22 @@
       <c r="D3" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="F3" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="H3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -1149,68 +1172,68 @@
         <v>33</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1263,10 +1286,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
@@ -1275,65 +1298,67 @@
         <v>33</v>
       </c>
       <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="G2" s="1"/>
       <c r="H2" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1388,10 +1413,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
@@ -1401,22 +1426,22 @@
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
@@ -1425,21 +1450,21 @@
         <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -1448,21 +1473,24 @@
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
@@ -1471,13 +1499,16 @@
         <v>33</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -1546,10 +1577,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
@@ -1558,20 +1589,23 @@
         <v>33</v>
       </c>
       <c r="E2" s="1"/>
+      <c r="F2" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
@@ -1579,19 +1613,22 @@
       <c r="D3" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="H3" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -1600,21 +1637,24 @@
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
@@ -1623,13 +1663,16 @@
         <v>33</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -1699,10 +1742,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
@@ -1711,20 +1754,23 @@
         <v>33</v>
       </c>
       <c r="E2" s="1"/>
+      <c r="F2" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
@@ -1732,19 +1778,22 @@
       <c r="D3" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="H3" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -1753,13 +1802,16 @@
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
@@ -1835,86 +1887,98 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>122</v>
+      <c r="F3" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -1983,65 +2047,65 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E2" s="1"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="7:9" x14ac:dyDescent="0.25">

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -56,7 +56,7 @@
     <t>🧤</t>
   </si>
   <si>
-    <t>active</t>
+    <t>passive</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"偷竊",
@@ -132,6 +132,9 @@
     <t>🗡️</t>
   </si>
   <si>
+    <t>active</t>
+  </si>
+  <si>
     <t>atk</t>
   </si>
   <si>
@@ -184,9 +187,6 @@
   </si>
   <si>
     <t>⚔️</t>
-  </si>
-  <si>
-    <t>passive</t>
   </si>
   <si>
     <t>buff</t>
@@ -1118,81 +1118,81 @@
         <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>50</v>
@@ -1217,7 +1217,7 @@
         <v>55</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>50</v>
@@ -1292,10 +1292,10 @@
         <v>61</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
@@ -1317,7 +1317,7 @@
         <v>66</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>50</v>
@@ -1342,7 +1342,7 @@
         <v>71</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>50</v>
@@ -1419,10 +1419,10 @@
         <v>77</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
@@ -1444,10 +1444,10 @@
         <v>82</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>83</v>
@@ -1467,10 +1467,10 @@
         <v>87</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>88</v>
@@ -1493,10 +1493,10 @@
         <v>93</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>94</v>
@@ -1583,10 +1583,10 @@
         <v>99</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
@@ -1608,10 +1608,10 @@
         <v>103</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>62</v>
@@ -1631,10 +1631,10 @@
         <v>107</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>108</v>
@@ -1657,10 +1657,10 @@
         <v>112</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>113</v>
@@ -1748,10 +1748,10 @@
         <v>117</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
@@ -1773,10 +1773,10 @@
         <v>120</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>62</v>
@@ -1796,10 +1796,10 @@
         <v>123</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>124</v>
@@ -1893,7 +1893,7 @@
         <v>127</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>126</v>
@@ -1917,7 +1917,7 @@
         <v>132</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>126</v>
@@ -1940,7 +1940,7 @@
         <v>136</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>126</v>
@@ -1963,7 +1963,7 @@
         <v>140</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>126</v>
@@ -2053,7 +2053,7 @@
         <v>146</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>50</v>
@@ -2075,7 +2075,7 @@
         <v>150</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>50</v>
@@ -2095,7 +2095,7 @@
         <v>154</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>50</v>

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="158">
   <si>
     <t>id</t>
   </si>
@@ -138,7 +138,7 @@
     <t>atk</t>
   </si>
   <si>
-    <t>"cd":1</t>
+    <t>"range":1,"cd":1</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"斬擊",
@@ -231,7 +231,7 @@
     <t>🎯</t>
   </si>
   <si>
-    <t>"cd":3</t>
+    <t>"range":5,"cd":3</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"狙擊",
@@ -325,7 +325,7 @@
 "firewall"</t>
   </si>
   <si>
-    <t>"cd":4</t>
+    <t>"range":5,"cd":4</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"燃燒術",
@@ -345,7 +345,7 @@
     <t>"combustion"</t>
   </si>
   <si>
-    <t>"cd":6</t>
+    <t>"range":5,"cd":6</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"流星雨",
@@ -474,6 +474,9 @@
   </si>
   <si>
     <t>🧪</t>
+  </si>
+  <si>
+    <t>"cd":3</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"解毒",
@@ -1923,21 +1926,21 @@
         <v>126</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1946,21 +1949,21 @@
         <v>126</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
@@ -1969,16 +1972,16 @@
         <v>126</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -2047,10 +2050,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -2061,18 +2064,18 @@
       <c r="E2" s="1"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -2081,18 +2084,18 @@
         <v>50</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -2102,10 +2105,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="7:9" x14ac:dyDescent="0.25">

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="164">
   <si>
     <t>id</t>
   </si>
@@ -138,7 +138,7 @@
     <t>atk</t>
   </si>
   <si>
-    <t>"range":1,"cd":1</t>
+    <t>"pow":1.15,"flat":0,"range":1,"cd":1</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"斬擊",
@@ -155,6 +155,9 @@
     <t>📍</t>
   </si>
   <si>
+    <t>"pow":1.0,"flat":0,"pen":0.2,"range":1,"cd":1</t>
+  </si>
+  <si>
     <t xml:space="preserve">"lab":"刺擊",
 "des":"直線突刺。無視目標 20% 物理防禦。"</t>
   </si>
@@ -231,7 +234,7 @@
     <t>🎯</t>
   </si>
   <si>
-    <t>"range":5,"cd":3</t>
+    <t>"pow":2.5,"flat":0,"range":5,"cd":3</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"狙擊",
@@ -325,7 +328,7 @@
 "firewall"</t>
   </si>
   <si>
-    <t>"range":5,"cd":4</t>
+    <t>"pow":2.0,"flat":15,"elm":"fire","src":"int","range":5,"cd":4</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"燃燒術",
@@ -345,7 +348,7 @@
     <t>"combustion"</t>
   </si>
   <si>
-    <t>"range":5,"cd":6</t>
+    <t>"pow":2.5,"flat":20,"elm":"fire","src":"int","range":5,"cd":6</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"流星雨",
@@ -362,6 +365,9 @@
     <t>❄️</t>
   </si>
   <si>
+    <t>"pow":1.5,"flat":10,"elm":"ice","src":"int","range":5,"cd":3</t>
+  </si>
+  <si>
     <t xml:space="preserve">"lab":"冰箭術",
 "des":"單體冰錐。造成傷害並減速 30%。"</t>
   </si>
@@ -394,6 +400,9 @@
 "icewall"</t>
   </si>
   <si>
+    <t>"pow":2.0,"flat":15,"elm":"ice","src":"int","range":5,"cd":4</t>
+  </si>
+  <si>
     <t xml:space="preserve">"lab":"冰封術",
 "des":"將減速狀態轉為凍結，使敵方完全無法行動 3 秒。"</t>
   </si>
@@ -411,6 +420,9 @@
     <t>"deepfreeze"</t>
   </si>
   <si>
+    <t>"pow":2.5,"flat":20,"elm":"ice","src":"int","range":5,"cd":6</t>
+  </si>
+  <si>
     <t xml:space="preserve">"lab":"暴風雪",
 "des":"大範圍持續性傷害，並有 10% 機率直接凍結敵人。"</t>
   </si>
@@ -425,6 +437,9 @@
     <t>🐍</t>
   </si>
   <si>
+    <t>"pow":1.5,"flat":10,"elm":"poison","src":"int","range":5,"cd":3</t>
+  </si>
+  <si>
     <t xml:space="preserve">"lab":"毒箭術",
 "des":"遠程發射毒針，使目標進入每秒扣血的中毒狀態。"</t>
   </si>
@@ -447,6 +462,9 @@
   <si>
     <t xml:space="preserve">"poisondart",
 "poisonmist"</t>
+  </si>
+  <si>
+    <t>"pow":2.0,"flat":15,"elm":"poison","src":"int","range":5,"cd":4</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"毒素引爆",
@@ -1152,21 +1170,21 @@
         <v>34</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1175,68 +1193,68 @@
         <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1289,10 +1307,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -1302,66 +1320,66 @@
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1416,10 +1434,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -1429,22 +1447,22 @@
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -1453,21 +1471,21 @@
         <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1476,24 +1494,24 @@
         <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
@@ -1502,16 +1520,16 @@
         <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -1580,10 +1598,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -1593,22 +1611,22 @@
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -1617,21 +1635,21 @@
         <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1640,24 +1658,24 @@
         <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
@@ -1666,16 +1684,16 @@
         <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -1745,10 +1763,10 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -1758,22 +1776,22 @@
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -1782,21 +1800,21 @@
         <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1805,16 +1823,16 @@
         <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
@@ -1890,98 +1908,98 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="7:9" x14ac:dyDescent="0.25">
@@ -2050,65 +2068,65 @@
     </row>
     <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E2" s="1"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="7:9" x14ac:dyDescent="0.25">

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -328,7 +328,7 @@
 "firewall"</t>
   </si>
   <si>
-    <t>"pow":2.0,"flat":15,"elm":"fire","src":"int","range":5,"cd":4</t>
+    <t>"pow":2.0,"flat":15,"elm":"fire","src":"int","cd":4,"scope":"group","radius":2</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"燃燒術",

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -175,7 +175,7 @@
     <t>"slash","thrust"</t>
   </si>
   <si>
-    <t>"cd":3,"scope":"group","radius":1</t>
+    <t>"range":1,"cd":3,"scope":"group","radius":1</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"旋風斬",
@@ -328,7 +328,7 @@
 "firewall"</t>
   </si>
   <si>
-    <t>"pow":2.0,"flat":15,"elm":"fire","src":"int","cd":4,"scope":"group","radius":2</t>
+    <t>"range":5,"pow":2.0,"flat":15,"elm":"fire","src":"int","cd":4,"scope":"group","radius":2</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"燃燒術",

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -138,7 +138,7 @@
     <t>atk</t>
   </si>
   <si>
-    <t>"pow":1.15,"flat":0,"range":1,"cd":1</t>
+    <t>"pow":1.15,"flat":0,"range":1,"cd":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"斬擊",
@@ -155,7 +155,7 @@
     <t>📍</t>
   </si>
   <si>
-    <t>"pow":1.0,"flat":0,"pen":0.2,"range":1,"cd":1</t>
+    <t>"pow":1.0,"flat":0,"pen":0.2,"range":1,"cd":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"刺擊",
@@ -175,7 +175,7 @@
     <t>"slash","thrust"</t>
   </si>
   <si>
-    <t>"range":1,"cd":3,"scope":"group","radius":1</t>
+    <t>"range":1,"cd":3,"scope":"group","radius":1,"cast":{}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"旋風斬",
@@ -234,7 +234,7 @@
     <t>🎯</t>
   </si>
   <si>
-    <t>"pow":2.5,"flat":0,"range":5,"cd":3</t>
+    <t>"pow":2.5,"flat":0,"range":5,"cd":3,"travel":{"type":"ranged"}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"狙擊",
@@ -290,7 +290,7 @@
     <t>🔥</t>
   </si>
   <si>
-    <t>"scope":"single","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","sprite":{"img":"🔥","size":25,"deg":-90},"cast":"spell"</t>
+    <t>"scope":"single","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","travel":{"type":"spell","img":"🔥","size":25,"deg":-90}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"火球術",
@@ -307,7 +307,7 @@
     <t>🧱</t>
   </si>
   <si>
-    <t>"scope":"single","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","sprite":{"img":"icons:1","scl":1,"deg":-45},"cast":"spell"</t>
+    <t>"scope":"single","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","travel":{"type":"spell","img":"icons:1","scl":1,"deg":-45}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"火牆術",
@@ -328,7 +328,7 @@
 "firewall"</t>
   </si>
   <si>
-    <t>"range":5,"pow":2.0,"flat":15,"elm":"fire","src":"int","cd":4,"scope":"group","radius":2</t>
+    <t>"range":5,"pow":2.0,"flat":15,"elm":"fire","src":"int","cd":4,"scope":"group","radius":2,"cast":{}</t>
   </si>
   <si>
     <t xml:space="preserve">"lab":"燃燒術",

--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="750" yWindow="1185" windowWidth="19200" windowHeight="6450"/>
+    <workbookView xWindow="750" yWindow="1185" windowWidth="19200" windowHeight="6450" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="general" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="sword" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="archery" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="fire" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="ice" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="poison" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="support" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="enhancement" state="visible" r:id="rId11"/>
+    <sheet name="general" sheetId="1" r:id="rId1"/>
+    <sheet name="sword" sheetId="2" r:id="rId2"/>
+    <sheet name="archery" sheetId="3" r:id="rId3"/>
+    <sheet name="fire" sheetId="4" r:id="rId4"/>
+    <sheet name="ice" sheetId="5" r:id="rId5"/>
+    <sheet name="poison" sheetId="6" r:id="rId6"/>
+    <sheet name="support" sheetId="7" r:id="rId7"/>
+    <sheet name="enhancement" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="169">
   <si>
     <t>id</t>
   </si>
@@ -59,11 +59,11 @@
     <t>passive</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"偷竊",
+    <t>"lab":"偷竊",
 "des":"從 NPC 或怪物身上獲取財物。成功率視敏捷而定。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Stealing",
+    <t>"lab":"Stealing",
 "des":"從 NPC 或怪物身上獲取財物。成功率視敏捷而定。"</t>
   </si>
   <si>
@@ -73,11 +73,11 @@
     <t>🗝️</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"開鎖",
+    <t>"lab":"開鎖",
 "des":"破解寶箱或門鎖。解鎖更高難度的鎖具。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Lockpicking",
+    <t>"lab":"Lockpicking",
 "des":"破解寶箱或門鎖。解鎖更高難度的鎖具。"</t>
   </si>
   <si>
@@ -87,11 +87,11 @@
     <t>🔪</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"解剖",
+    <t>"lab":"解剖",
 "des":"分解動物屍體，取得肉類、皮毛與骨頭...等可用素材。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Butcher",
+    <t>"lab":"Butcher",
 "des":"分解動物屍體，取得肉類、皮毛與骨頭...等可用素材。"</t>
   </si>
   <si>
@@ -101,11 +101,11 @@
     <t>👤</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"潛行",
+    <t>"lab":"潛行",
 "des":"進入半透明狀態，大幅降低敵方偵測範圍。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Stealth",
+    <t>"lab":"Stealth",
 "des":"進入半透明狀態，大幅降低敵方偵測範圍。"</t>
   </si>
   <si>
@@ -115,11 +115,11 @@
     <t>💰</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"討價還價",
+    <t>"lab":"討價還價",
 "des":"交易時獲得更好價格。商店售價 -15%，回收價 +15%。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Barter",
+    <t>"lab":"Barter",
 "des":"交易時獲得更好價格。商店售價 -15%，回收價 +15%。"</t>
   </si>
   <si>
@@ -141,11 +141,11 @@
     <t>"pow":1.15,"flat":0,"range":1,"cd":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"斬擊",
+    <t>"lab":"斬擊",
 "des":"基本橫劈，對前方弧形範圍造成 115% 傷害。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Slash",
+    <t>"lab":"Slash",
 "des":"基本橫劈，對前方弧形範圍造成 115% 傷害。"</t>
   </si>
   <si>
@@ -158,11 +158,11 @@
     <t>"pow":1.0,"flat":0,"pen":0.2,"range":1,"cd":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"刺擊",
+    <t>"lab":"刺擊",
 "des":"直線突刺。無視目標 20% 物理防禦。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Thrust",
+    <t>"lab":"Thrust",
 "des":"直線突刺。無視目標 20% 物理防禦。"</t>
   </si>
   <si>
@@ -175,14 +175,14 @@
     <t>"slash","thrust"</t>
   </si>
   <si>
-    <t>"range":1,"cd":3,"scope":"group","radius":1,"cast":{}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"旋風斬",
+    <t>"range":1,"cd":3,"scope":"group","radius":1,"cast":{},"fx":{}</t>
+  </si>
+  <si>
+    <t>"lab":"旋風斬",
 "des":"旋轉劍身，對周圍全體造成多段傷害。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Whirlwind",
+    <t>"lab":"Whirlwind",
 "des":"旋轉劍身，對周圍全體造成多段傷害。"</t>
   </si>
   <si>
@@ -195,15 +195,15 @@
     <t>buff</t>
   </si>
   <si>
-    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.1,"reqClass":"sword"},
+    <t>{"type":"mod","key":"acc","a":0.1,"reqClass":"sword"},
 {"type":"mod","key":"atk","m":0.1,"reqClass":"sword"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"劍術專家",
+    <t>"lab":"劍術專家",
 "des":"精通劍術。裝備劍類武器時，命中+10%、攻擊力+10%。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Sword Expertise",
+    <t>"lab":"Sword Expertise",
 "des":"Mastery of swordsmanship. +10% accuracy and +10% attack power while wielding a sword."</t>
   </si>
   <si>
@@ -216,15 +216,15 @@
     <t>"swordmastery"</t>
   </si>
   <si>
-    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.15,"reqClass":"sword"},
+    <t>{"type":"mod","key":"acc","a":0.15,"reqClass":"sword"},
 {"type":"mod","key":"atk","m":0.15,"reqClass":"sword"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"劍術大師",
+    <t>"lab":"劍術大師",
 "des":"劍術造詣爐火純青。裝備劍類武器時，命中與攻擊力再進一步大幅提升。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Sword Mastery",
+    <t>"lab":"Sword Mastery",
 "des":"Peak swordsmanship. Further boosts accuracy and attack power while wielding a sword."</t>
   </si>
   <si>
@@ -237,11 +237,11 @@
     <t>"pow":2.5,"flat":0,"range":5,"cd":3,"travel":{"type":"ranged"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"狙擊",
+    <t>"lab":"狙擊",
 "des":"瞄準敵人的弱點射擊，造成 250% 的傷害。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Snipe",
+    <t>"lab":"Snipe",
 "des":"瞄準敵人的弱點射擊，造成 250% 的傷害。"</t>
   </si>
   <si>
@@ -251,15 +251,15 @@
     <t>🏹</t>
   </si>
   <si>
-    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.1,"reqClass":"bow"},
+    <t>{"type":"mod","key":"acc","a":0.1,"reqClass":"bow"},
 {"type":"mod","key":"atk","m":0.1,"reqClass":"bow"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"弓箭專家",
+    <t>"lab":"弓箭專家",
 "des":"精通弓術。裝備弓類武器時，命中+10%、攻擊力+10%。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Archery Expertise",
+    <t>"lab":"Archery Expertise",
 "des":"Mastery of archery. +10% accuracy and +10% attack power while wielding a bow."</t>
   </si>
   <si>
@@ -272,15 +272,15 @@
     <t>"archeryexpert"</t>
   </si>
   <si>
-    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.15,"reqClass":"bow"},
+    <t>{"type":"mod","key":"acc","a":0.15,"reqClass":"bow"},
 {"type":"mod","key":"atk","m":0.15,"reqClass":"bow"}</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"弓箭大師",
+    <t>"lab":"弓箭大師",
 "des":"弓術造詣爐火純青。裝備弓類武器時，命中與攻擊力再進一步大幅提升。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Archery Mastery",
+    <t>"lab":"Archery Mastery",
 "des":"Peak archery. Further boosts accuracy and attack power while wielding a bow."</t>
   </si>
   <si>
@@ -290,14 +290,14 @@
     <t>🔥</t>
   </si>
   <si>
-    <t>"scope":"single","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","travel":{"type":"spell","img":"🔥","size":25,"deg":-90}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"火球術",
+    <t>"scope":"single","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
+  </si>
+  <si>
+    <t>"lab":"火球術",
 "des":"投擲火球。造成基礎火屬性爆炸傷害。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Fireball",
+    <t>"lab":"Fireball",
 "des":"投擲火球。造成基礎火屬性爆炸傷害。"</t>
   </si>
   <si>
@@ -307,14 +307,14 @@
     <t>🧱</t>
   </si>
   <si>
-    <t>"scope":"single","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","travel":{"type":"spell","img":"icons:1","scl":1,"deg":-45}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"火牆術",
+    <t>"scope":"single","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","travel":{"type":"spell","img":"icons:1","scl":1,"deg":-45},"fx":{}</t>
+  </si>
+  <si>
+    <t>"lab":"火牆術",
 "des":"召喚火焰地帶。對經過者施加持續灼燒。"</t>
   </si>
   <si>
-    <t xml:space="preserve">"lab":"Fire Wall",
+    <t>"lab":"Fire Wall",
 "des":"召喚火焰地帶。對經過者施加持續灼燒。"</t>
   </si>
   <si>
@@ -324,282 +324,309 @@
     <t>🌋</t>
   </si>
   <si>
-    <t xml:space="preserve">"fireball",
+    <t>"range":5,"pow":2.0,"flat":15,"elm":"fire","src":"int","cd":4,"scope":"group","radius":2,"cast":{},"fx":{}</t>
+  </si>
+  <si>
+    <t>"lab":"燃燒術",
+"des":"引爆目標身上的灼燒狀態，造成瞬間大傷害。"</t>
+  </si>
+  <si>
+    <t>"lab":"Combustion",
+"des":"引爆目標身上的灼燒狀態，造成瞬間大傷害。"</t>
+  </si>
+  <si>
+    <t>meteorshower</t>
+  </si>
+  <si>
+    <t>☄️</t>
+  </si>
+  <si>
+    <t>"combustion"</t>
+  </si>
+  <si>
+    <t>"pow":2.5,"flat":20,"elm":"fire","src":"int","range":5,"cd":6</t>
+  </si>
+  <si>
+    <t>"lab":"流星雨",
+"des":"大範圍隕石轟炸，摧毀範圍內一切。"</t>
+  </si>
+  <si>
+    <t>"lab":"Meteor Shower",
+"des":"大範圍隕石轟炸，摧毀範圍內一切。"</t>
+  </si>
+  <si>
+    <t>"scope":"group","radius":2,"pow":1.8,"flat":10,"elm":"fire","src":"int","cd":5,"travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
+  </si>
+  <si>
+    <t>"lab":"高級火球術",
+"des":"對自身周圍範圍內的敵人各自發射火球，造成範圍傷害。"</t>
+  </si>
+  <si>
+    <t>"lab":"Greater Fireball",
+"des":"Fires a fireball at each enemy within range around yourself."</t>
+  </si>
+  <si>
+    <t>icebolt</t>
+  </si>
+  <si>
+    <t>❄️</t>
+  </si>
+  <si>
+    <t>"pow":1.5,"flat":10,"elm":"ice","src":"int","range":5,"cd":3</t>
+  </si>
+  <si>
+    <t>"lab":"冰箭術",
+"des":"單體冰錐。造成傷害並減速 30%。"</t>
+  </si>
+  <si>
+    <t>"lab":"Ice Bolt",
+"des":"單體冰錐。造成傷害並減速 30%。"</t>
+  </si>
+  <si>
+    <t>icewall</t>
+  </si>
+  <si>
+    <t>🧊</t>
+  </si>
+  <si>
+    <t>"lab":"冰牆術",
+"des":"召喚可抵擋飛行道具的冰塊物理障礙物。"</t>
+  </si>
+  <si>
+    <t>"lab":"Ice Wall",
+"des":"召喚可抵擋飛行道具的冰塊物理障礙物。"</t>
+  </si>
+  <si>
+    <t>deepfreeze</t>
+  </si>
+  <si>
+    <t>🥶</t>
+  </si>
+  <si>
+    <t>"icebolt",
+"icewall"</t>
+  </si>
+  <si>
+    <t>"pow":2.0,"flat":15,"elm":"ice","src":"int","range":5,"cd":4</t>
+  </si>
+  <si>
+    <t>"lab":"冰封術",
+"des":"將減速狀態轉為凍結，使敵方完全無法行動 3 秒。"</t>
+  </si>
+  <si>
+    <t>"lab":"Deep Freeze",
+"des":"將減速狀態轉為凍結，使敵方完全無法行動 3 秒。"</t>
+  </si>
+  <si>
+    <t>blizzard</t>
+  </si>
+  <si>
+    <t>🌨️</t>
+  </si>
+  <si>
+    <t>"deepfreeze"</t>
+  </si>
+  <si>
+    <t>"pow":2.5,"flat":20,"elm":"ice","src":"int","range":5,"cd":6</t>
+  </si>
+  <si>
+    <t>"lab":"暴風雪",
+"des":"大範圍持續性傷害，並有 10% 機率直接凍結敵人。"</t>
+  </si>
+  <si>
+    <t>"lab":"Blizzard",
+"des":"大範圍持續性傷害，並有 10% 機率直接凍結敵人。"</t>
+  </si>
+  <si>
+    <t>poisondart</t>
+  </si>
+  <si>
+    <t>🐍</t>
+  </si>
+  <si>
+    <t>"pow":1.5,"flat":10,"elm":"poison","src":"int","range":5,"cd":3</t>
+  </si>
+  <si>
+    <t>"lab":"毒箭術",
+"des":"遠程發射毒針，使目標進入每秒扣血的中毒狀態。"</t>
+  </si>
+  <si>
+    <t>poisonmist</t>
+  </si>
+  <si>
+    <t>🌫️</t>
+  </si>
+  <si>
+    <t>"lab":"毒霧術",
+"des":"在指定區域散佈致命毒氣。"</t>
+  </si>
+  <si>
+    <t>venomburst</t>
+  </si>
+  <si>
+    <t>🍄</t>
+  </si>
+  <si>
+    <t>"poisondart",
+"poisonmist"</t>
+  </si>
+  <si>
+    <t>"pow":2.0,"flat":15,"elm":"poison","src":"int","range":5,"cd":4</t>
+  </si>
+  <si>
+    <t>"lab":"毒素引爆",
+"des":"使受毒者爆炸，將毒素噴濺至周圍目標。"</t>
+  </si>
+  <si>
+    <t>heal</t>
+  </si>
+  <si>
+    <t>💖</t>
+  </si>
+  <si>
+    <t>"cd":2</t>
+  </si>
+  <si>
+    <t>"lab":"治療",
+"des":"恢復目標生命值。"</t>
+  </si>
+  <si>
+    <t>"lab":"Heal",
+"des":"恢復目標生命值。"</t>
+  </si>
+  <si>
+    <t>cure</t>
+  </si>
+  <si>
+    <t>🧪</t>
+  </si>
+  <si>
+    <t>"cd":3</t>
+  </si>
+  <si>
+    <t>"lab":"解毒",
+"des":"清除體內毒素。"</t>
+  </si>
+  <si>
+    <t>"lab":"Cure",
+"des":"清除體內毒素。"</t>
+  </si>
+  <si>
+    <t>holylight</t>
+  </si>
+  <si>
+    <t>☀️</t>
+  </si>
+  <si>
+    <t>"lab":"聖光",
+"des":"移除 1 個負面狀態。"</t>
+  </si>
+  <si>
+    <t>"lab":"Holy Light",
+"des":"移除 1 個負面狀態。"</t>
+  </si>
+  <si>
+    <t>purify</t>
+  </si>
+  <si>
+    <t>✨</t>
+  </si>
+  <si>
+    <t>"cure",
+"holylight"</t>
+  </si>
+  <si>
+    <t>"cd":5</t>
+  </si>
+  <si>
+    <t>"lab":"淨化",
+"des":"清除體內毒素，移除所有負面狀態。"</t>
+  </si>
+  <si>
+    <t>"lab":"Purify",
+"des":"清除體內毒素，移除所有負面狀態。"</t>
+  </si>
+  <si>
+    <t>strboost</t>
+  </si>
+  <si>
+    <t>💪</t>
+  </si>
+  <si>
+    <t>"lab":"力量增強",
+"des":"增加力量，可提升近戰傷害。"</t>
+  </si>
+  <si>
+    <t>"lab":"Strength Boost",
+"des":"增加力量，可提升近戰傷害。"</t>
+  </si>
+  <si>
+    <t>agiboost</t>
+  </si>
+  <si>
+    <t>👟</t>
+  </si>
+  <si>
+    <t>"lab":"敏捷增強",
+"des":"增加敏捷，可提升閃避。"</t>
+  </si>
+  <si>
+    <t>"lab":"Agility Boost",
+"des":"增加敏捷，可提升閃避。"</t>
+  </si>
+  <si>
+    <t>intboost</t>
+  </si>
+  <si>
+    <t>🧠</t>
+  </si>
+  <si>
+    <t>"lab":"智力增強",
+"des":"增加智力，可提升法術效果。"</t>
+  </si>
+  <si>
+    <t>"lab":"Intelligence Boost",
+"des":"增加智力，可提升法術效果。"</t>
+  </si>
+  <si>
+    <t>fireballvolley</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>"fireball"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>"fireballvolley",
 "firewall"</t>
-  </si>
-  <si>
-    <t>"range":5,"pow":2.0,"flat":15,"elm":"fire","src":"int","cd":4,"scope":"group","radius":2,"cast":{}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"燃燒術",
-"des":"引爆目標身上的灼燒狀態，造成瞬間大傷害。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Combustion",
-"des":"引爆目標身上的灼燒狀態，造成瞬間大傷害。"</t>
-  </si>
-  <si>
-    <t>meteorshower</t>
-  </si>
-  <si>
-    <t>☄️</t>
-  </si>
-  <si>
-    <t>"combustion"</t>
-  </si>
-  <si>
-    <t>"pow":2.5,"flat":20,"elm":"fire","src":"int","range":5,"cd":6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"流星雨",
-"des":"大範圍隕石轟炸，摧毀範圍內一切。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Meteor Shower",
-"des":"大範圍隕石轟炸，摧毀範圍內一切。"</t>
-  </si>
-  <si>
-    <t>icebolt</t>
-  </si>
-  <si>
-    <t>❄️</t>
-  </si>
-  <si>
-    <t>"pow":1.5,"flat":10,"elm":"ice","src":"int","range":5,"cd":3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"冰箭術",
-"des":"單體冰錐。造成傷害並減速 30%。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Ice Bolt",
-"des":"單體冰錐。造成傷害並減速 30%。"</t>
-  </si>
-  <si>
-    <t>icewall</t>
-  </si>
-  <si>
-    <t>🧊</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"冰牆術",
-"des":"召喚可抵擋飛行道具的冰塊物理障礙物。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Ice Wall",
-"des":"召喚可抵擋飛行道具的冰塊物理障礙物。"</t>
-  </si>
-  <si>
-    <t>deepfreeze</t>
-  </si>
-  <si>
-    <t>🥶</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"icebolt",
-"icewall"</t>
-  </si>
-  <si>
-    <t>"pow":2.0,"flat":15,"elm":"ice","src":"int","range":5,"cd":4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"冰封術",
-"des":"將減速狀態轉為凍結，使敵方完全無法行動 3 秒。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Deep Freeze",
-"des":"將減速狀態轉為凍結，使敵方完全無法行動 3 秒。"</t>
-  </si>
-  <si>
-    <t>blizzard</t>
-  </si>
-  <si>
-    <t>🌨️</t>
-  </si>
-  <si>
-    <t>"deepfreeze"</t>
-  </si>
-  <si>
-    <t>"pow":2.5,"flat":20,"elm":"ice","src":"int","range":5,"cd":6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"暴風雪",
-"des":"大範圍持續性傷害，並有 10% 機率直接凍結敵人。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Blizzard",
-"des":"大範圍持續性傷害，並有 10% 機率直接凍結敵人。"</t>
-  </si>
-  <si>
-    <t>poisondart</t>
-  </si>
-  <si>
-    <t>🐍</t>
-  </si>
-  <si>
-    <t>"pow":1.5,"flat":10,"elm":"poison","src":"int","range":5,"cd":3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"毒箭術",
-"des":"遠程發射毒針，使目標進入每秒扣血的中毒狀態。"</t>
-  </si>
-  <si>
-    <t>poisonmist</t>
-  </si>
-  <si>
-    <t>🌫️</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"毒霧術",
-"des":"在指定區域散佈致命毒氣。"</t>
-  </si>
-  <si>
-    <t>venomburst</t>
-  </si>
-  <si>
-    <t>🍄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"poisondart",
-"poisonmist"</t>
-  </si>
-  <si>
-    <t>"pow":2.0,"flat":15,"elm":"poison","src":"int","range":5,"cd":4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"毒素引爆",
-"des":"使受毒者爆炸，將毒素噴濺至周圍目標。"</t>
-  </si>
-  <si>
-    <t>heal</t>
-  </si>
-  <si>
-    <t>💖</t>
-  </si>
-  <si>
-    <t>"cd":2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"治療",
-"des":"恢復目標生命值。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Heal",
-"des":"恢復目標生命值。"</t>
-  </si>
-  <si>
-    <t>cure</t>
-  </si>
-  <si>
-    <t>🧪</t>
-  </si>
-  <si>
-    <t>"cd":3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"解毒",
-"des":"清除體內毒素。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Cure",
-"des":"清除體內毒素。"</t>
-  </si>
-  <si>
-    <t>holylight</t>
-  </si>
-  <si>
-    <t>☀️</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"聖光",
-"des":"移除 1 個負面狀態。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Holy Light",
-"des":"移除 1 個負面狀態。"</t>
-  </si>
-  <si>
-    <t>purify</t>
-  </si>
-  <si>
-    <t>✨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"cure",
-"holylight"</t>
-  </si>
-  <si>
-    <t>"cd":5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"淨化",
-"des":"清除體內毒素，移除所有負面狀態。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Purify",
-"des":"清除體內毒素，移除所有負面狀態。"</t>
-  </si>
-  <si>
-    <t>strboost</t>
-  </si>
-  <si>
-    <t>💪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"力量增強",
-"des":"增加力量，可提升近戰傷害。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Strength Boost",
-"des":"增加力量，可提升近戰傷害。"</t>
-  </si>
-  <si>
-    <t>agiboost</t>
-  </si>
-  <si>
-    <t>👟</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"敏捷增強",
-"des":"增加敏捷，可提升閃避。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Agility Boost",
-"des":"增加敏捷，可提升閃避。"</t>
-  </si>
-  <si>
-    <t>intboost</t>
-  </si>
-  <si>
-    <t>🧠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"智力增強",
-"des":"增加智力，可提升法術效果。"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"lab":"Intelligence Boost",
-"des":"增加智力，可提升法術效果。"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體 Light"/>
+      <family val="2"/>
       <charset val="136"/>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="微軟正黑體 Light"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -632,7 +659,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -931,22 +958,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.25" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="64.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="67.25" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="64.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="67.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -975,7 +1003,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -988,7 +1016,6 @@
       <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
         <v>12</v>
@@ -997,7 +1024,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="31.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1017,7 +1044,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="31.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -1038,7 +1065,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="31.5" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -1055,7 +1082,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="31.5" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
@@ -1073,36 +1100,37 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="H7" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
+    <row r="13" spans="1:9">
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
-    <col min="2" max="4" width="8.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5" style="1" customWidth="1"/>
-    <col min="8" max="9" width="66.375" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
+    <col min="2" max="4" width="8.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="66.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1131,7 +1159,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
@@ -1144,11 +1172,9 @@
       <c r="D2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="1"/>
       <c r="H2" s="2" t="s">
         <v>36</v>
       </c>
@@ -1156,7 +1182,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="31.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>38</v>
       </c>
@@ -1179,7 +1205,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="31.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>43</v>
       </c>
@@ -1205,7 +1231,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="31.5" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>49</v>
       </c>
@@ -1218,8 +1244,6 @@
       <c r="D5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
         <v>52</v>
       </c>
@@ -1230,7 +1254,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="31.5" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>55</v>
       </c>
@@ -1246,7 +1270,6 @@
       <c r="E6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
         <v>58</v>
       </c>
@@ -1258,25 +1281,27 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
-    <col min="2" max="5" width="8.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5" style="1" customWidth="1"/>
-    <col min="8" max="9" width="66.375" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
+    <col min="2" max="5" width="8.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="66.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1305,7 +1330,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>61</v>
       </c>
@@ -1318,11 +1343,9 @@
       <c r="D2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="1"/>
       <c r="H2" s="2" t="s">
         <v>64</v>
       </c>
@@ -1330,7 +1353,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="31.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>66</v>
       </c>
@@ -1343,8 +1366,6 @@
       <c r="D3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
         <v>68</v>
       </c>
@@ -1355,7 +1376,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="31.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>71</v>
       </c>
@@ -1371,7 +1392,6 @@
       <c r="E4" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
         <v>74</v>
       </c>
@@ -1383,27 +1403,29 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="18.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.25" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="59.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="59.5703125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1432,7 +1454,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>77</v>
       </c>
@@ -1445,7 +1467,6 @@
       <c r="D2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
         <v>79</v>
       </c>
@@ -1457,7 +1478,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="31.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>82</v>
       </c>
@@ -1480,12 +1501,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="31.5" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1493,25 +1514,26 @@
       <c r="D4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>89</v>
+      <c r="E4" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>90</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="31.5" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
@@ -1519,55 +1541,78 @@
       <c r="D5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="F13" s="2" t="s">
+    </row>
+    <row r="8" spans="1:9">
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="F14" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="18.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.25" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1596,12 +1641,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -1609,24 +1654,23 @@
       <c r="D2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="31.5" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -1635,21 +1679,21 @@
         <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="31.5" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1658,24 +1702,24 @@
         <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="31.5" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
@@ -1684,55 +1728,56 @@
         <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="7:9" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
+    <row r="13" spans="1:9">
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="18.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.25" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="61" style="1" customWidth="1"/>
     <col min="9" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1761,12 +1806,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -1774,24 +1819,23 @@
       <c r="D2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="1"/>
       <c r="F2" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="31.5" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -1800,21 +1844,21 @@
         <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="31.5" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1823,61 +1867,62 @@
         <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="16.5" customHeight="1">
       <c r="F5" s="1"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
+    <row r="13" spans="1:9">
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="18.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.25" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="14" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="48.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="48.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1906,138 +1951,139 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="31.5" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="31.5" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="6" spans="7:9" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
+    <row r="13" spans="1:9">
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.875" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="23.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.25" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="9" width="46" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2066,12 +2112,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -2079,21 +2125,20 @@
       <c r="D2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="1"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="31.5" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -2102,18 +2147,18 @@
         <v>51</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="31.5" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -2123,29 +2168,29 @@
       </c>
       <c r="E4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="5" spans="7:9" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
+    <row r="12" spans="1:9">
       <c r="F12" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/xls/ability.xlsx
+++ b/xls/ability.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="750" yWindow="1185" windowWidth="19200" windowHeight="6450" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="general" sheetId="1" r:id="rId1"/>
-    <sheet name="sword" sheetId="2" r:id="rId2"/>
-    <sheet name="archery" sheetId="3" r:id="rId3"/>
-    <sheet name="fire" sheetId="4" r:id="rId4"/>
-    <sheet name="ice" sheetId="5" r:id="rId5"/>
-    <sheet name="poison" sheetId="6" r:id="rId6"/>
-    <sheet name="support" sheetId="7" r:id="rId7"/>
-    <sheet name="enhancement" sheetId="8" r:id="rId8"/>
+    <sheet sheetId="1" name="general" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="sword" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="archery" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="fire" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="ice" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="poison" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="support" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="enhancement" state="visible" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -59,11 +59,11 @@
     <t>passive</t>
   </si>
   <si>
-    <t>"lab":"偷竊",
+    <t xml:space="preserve">"lab":"偷竊",
 "des":"從 NPC 或怪物身上獲取財物。成功率視敏捷而定。"</t>
   </si>
   <si>
-    <t>"lab":"Stealing",
+    <t xml:space="preserve">"lab":"Stealing",
 "des":"從 NPC 或怪物身上獲取財物。成功率視敏捷而定。"</t>
   </si>
   <si>
@@ -73,11 +73,11 @@
     <t>🗝️</t>
   </si>
   <si>
-    <t>"lab":"開鎖",
+    <t xml:space="preserve">"lab":"開鎖",
 "des":"破解寶箱或門鎖。解鎖更高難度的鎖具。"</t>
   </si>
   <si>
-    <t>"lab":"Lockpicking",
+    <t xml:space="preserve">"lab":"Lockpicking",
 "des":"破解寶箱或門鎖。解鎖更高難度的鎖具。"</t>
   </si>
   <si>
@@ -87,11 +87,11 @@
     <t>🔪</t>
   </si>
   <si>
-    <t>"lab":"解剖",
+    <t xml:space="preserve">"lab":"解剖",
 "des":"分解動物屍體，取得肉類、皮毛與骨頭...等可用素材。"</t>
   </si>
   <si>
-    <t>"lab":"Butcher",
+    <t xml:space="preserve">"lab":"Butcher",
 "des":"分解動物屍體，取得肉類、皮毛與骨頭...等可用素材。"</t>
   </si>
   <si>
@@ -101,11 +101,11 @@
     <t>👤</t>
   </si>
   <si>
-    <t>"lab":"潛行",
+    <t xml:space="preserve">"lab":"潛行",
 "des":"進入半透明狀態，大幅降低敵方偵測範圍。"</t>
   </si>
   <si>
-    <t>"lab":"Stealth",
+    <t xml:space="preserve">"lab":"Stealth",
 "des":"進入半透明狀態，大幅降低敵方偵測範圍。"</t>
   </si>
   <si>
@@ -115,11 +115,11 @@
     <t>💰</t>
   </si>
   <si>
-    <t>"lab":"討價還價",
+    <t xml:space="preserve">"lab":"討價還價",
 "des":"交易時獲得更好價格。商店售價 -15%，回收價 +15%。"</t>
   </si>
   <si>
-    <t>"lab":"Barter",
+    <t xml:space="preserve">"lab":"Barter",
 "des":"交易時獲得更好價格。商店售價 -15%，回收價 +15%。"</t>
   </si>
   <si>
@@ -141,11 +141,11 @@
     <t>"pow":1.15,"flat":0,"range":1,"cd":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
-    <t>"lab":"斬擊",
+    <t xml:space="preserve">"lab":"斬擊",
 "des":"基本橫劈，對前方弧形範圍造成 115% 傷害。"</t>
   </si>
   <si>
-    <t>"lab":"Slash",
+    <t xml:space="preserve">"lab":"Slash",
 "des":"基本橫劈，對前方弧形範圍造成 115% 傷害。"</t>
   </si>
   <si>
@@ -158,11 +158,11 @@
     <t>"pow":1.0,"flat":0,"pen":0.2,"range":1,"cd":1,"travel":{"type":"melee"}</t>
   </si>
   <si>
-    <t>"lab":"刺擊",
+    <t xml:space="preserve">"lab":"刺擊",
 "des":"直線突刺。無視目標 20% 物理防禦。"</t>
   </si>
   <si>
-    <t>"lab":"Thrust",
+    <t xml:space="preserve">"lab":"Thrust",
 "des":"直線突刺。無視目標 20% 物理防禦。"</t>
   </si>
   <si>
@@ -178,11 +178,11 @@
     <t>"range":1,"cd":3,"scope":"group","radius":1,"cast":{},"fx":{}</t>
   </si>
   <si>
-    <t>"lab":"旋風斬",
+    <t xml:space="preserve">"lab":"旋風斬",
 "des":"旋轉劍身，對周圍全體造成多段傷害。"</t>
   </si>
   <si>
-    <t>"lab":"Whirlwind",
+    <t xml:space="preserve">"lab":"Whirlwind",
 "des":"旋轉劍身，對周圍全體造成多段傷害。"</t>
   </si>
   <si>
@@ -195,15 +195,15 @@
     <t>buff</t>
   </si>
   <si>
-    <t>{"type":"mod","key":"acc","a":0.1,"reqClass":"sword"},
+    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.1,"reqClass":"sword"},
 {"type":"mod","key":"atk","m":0.1,"reqClass":"sword"}</t>
   </si>
   <si>
-    <t>"lab":"劍術專家",
+    <t xml:space="preserve">"lab":"劍術專家",
 "des":"精通劍術。裝備劍類武器時，命中+10%、攻擊力+10%。"</t>
   </si>
   <si>
-    <t>"lab":"Sword Expertise",
+    <t xml:space="preserve">"lab":"Sword Expertise",
 "des":"Mastery of swordsmanship. +10% accuracy and +10% attack power while wielding a sword."</t>
   </si>
   <si>
@@ -216,15 +216,15 @@
     <t>"swordmastery"</t>
   </si>
   <si>
-    <t>{"type":"mod","key":"acc","a":0.15,"reqClass":"sword"},
+    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.15,"reqClass":"sword"},
 {"type":"mod","key":"atk","m":0.15,"reqClass":"sword"}</t>
   </si>
   <si>
-    <t>"lab":"劍術大師",
+    <t xml:space="preserve">"lab":"劍術大師",
 "des":"劍術造詣爐火純青。裝備劍類武器時，命中與攻擊力再進一步大幅提升。"</t>
   </si>
   <si>
-    <t>"lab":"Sword Mastery",
+    <t xml:space="preserve">"lab":"Sword Mastery",
 "des":"Peak swordsmanship. Further boosts accuracy and attack power while wielding a sword."</t>
   </si>
   <si>
@@ -237,11 +237,11 @@
     <t>"pow":2.5,"flat":0,"range":5,"cd":3,"travel":{"type":"ranged"}</t>
   </si>
   <si>
-    <t>"lab":"狙擊",
+    <t xml:space="preserve">"lab":"狙擊",
 "des":"瞄準敵人的弱點射擊，造成 250% 的傷害。"</t>
   </si>
   <si>
-    <t>"lab":"Snipe",
+    <t xml:space="preserve">"lab":"Snipe",
 "des":"瞄準敵人的弱點射擊，造成 250% 的傷害。"</t>
   </si>
   <si>
@@ -251,15 +251,15 @@
     <t>🏹</t>
   </si>
   <si>
-    <t>{"type":"mod","key":"acc","a":0.1,"reqClass":"bow"},
+    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.1,"reqClass":"bow"},
 {"type":"mod","key":"atk","m":0.1,"reqClass":"bow"}</t>
   </si>
   <si>
-    <t>"lab":"弓箭專家",
+    <t xml:space="preserve">"lab":"弓箭專家",
 "des":"精通弓術。裝備弓類武器時，命中+10%、攻擊力+10%。"</t>
   </si>
   <si>
-    <t>"lab":"Archery Expertise",
+    <t xml:space="preserve">"lab":"Archery Expertise",
 "des":"Mastery of archery. +10% accuracy and +10% attack power while wielding a bow."</t>
   </si>
   <si>
@@ -272,15 +272,15 @@
     <t>"archeryexpert"</t>
   </si>
   <si>
-    <t>{"type":"mod","key":"acc","a":0.15,"reqClass":"bow"},
+    <t xml:space="preserve">{"type":"mod","key":"acc","a":0.15,"reqClass":"bow"},
 {"type":"mod","key":"atk","m":0.15,"reqClass":"bow"}</t>
   </si>
   <si>
-    <t>"lab":"弓箭大師",
+    <t xml:space="preserve">"lab":"弓箭大師",
 "des":"弓術造詣爐火純青。裝備弓類武器時，命中與攻擊力再進一步大幅提升。"</t>
   </si>
   <si>
-    <t>"lab":"Archery Mastery",
+    <t xml:space="preserve">"lab":"Archery Mastery",
 "des":"Peak archery. Further boosts accuracy and attack power while wielding a bow."</t>
   </si>
   <si>
@@ -293,11 +293,11 @@
     <t>"scope":"single","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
   </si>
   <si>
-    <t>"lab":"火球術",
+    <t xml:space="preserve">"lab":"火球術",
 "des":"投擲火球。造成基礎火屬性爆炸傷害。"</t>
   </si>
   <si>
-    <t>"lab":"Fireball",
+    <t xml:space="preserve">"lab":"Fireball",
 "des":"投擲火球。造成基礎火屬性爆炸傷害。"</t>
   </si>
   <si>
@@ -310,28 +310,49 @@
     <t>"scope":"single","cd":3,"range":5,"pow":1.5,"flat":10,"elm":"fire","src":"int","travel":{"type":"spell","img":"icons:1","scl":1,"deg":-45},"fx":{}</t>
   </si>
   <si>
-    <t>"lab":"火牆術",
+    <t xml:space="preserve">"lab":"火牆術",
 "des":"召喚火焰地帶。對經過者施加持續灼燒。"</t>
   </si>
   <si>
-    <t>"lab":"Fire Wall",
+    <t xml:space="preserve">"lab":"Fire Wall",
 "des":"召喚火焰地帶。對經過者施加持續灼燒。"</t>
   </si>
   <si>
+    <t>fireballvolley</t>
+  </si>
+  <si>
+    <t>"fireball"</t>
+  </si>
+  <si>
+    <t>"scope":"group","radius":2,"pow":1.8,"flat":10,"elm":"fire","src":"int","cd":5,"travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab":"高級火球術",
+"des":"對自身周圍範圍內的敵人各自發射火球，造成範圍傷害。"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab":"Greater Fireball",
+"des":"Fires a fireball at each enemy within range around yourself."</t>
+  </si>
+  <si>
     <t>combustion</t>
   </si>
   <si>
     <t>🌋</t>
   </si>
   <si>
+    <t xml:space="preserve">"fireballvolley",
+"firewall"</t>
+  </si>
+  <si>
     <t>"range":5,"pow":2.0,"flat":15,"elm":"fire","src":"int","cd":4,"scope":"group","radius":2,"cast":{},"fx":{}</t>
   </si>
   <si>
-    <t>"lab":"燃燒術",
+    <t xml:space="preserve">"lab":"燃燒術",
 "des":"引爆目標身上的灼燒狀態，造成瞬間大傷害。"</t>
   </si>
   <si>
-    <t>"lab":"Combustion",
+    <t xml:space="preserve">"lab":"Combustion",
 "des":"引爆目標身上的灼燒狀態，造成瞬間大傷害。"</t>
   </si>
   <si>
@@ -344,28 +365,17 @@
     <t>"combustion"</t>
   </si>
   <si>
-    <t>"pow":2.5,"flat":20,"elm":"fire","src":"int","range":5,"cd":6</t>
-  </si>
-  <si>
-    <t>"lab":"流星雨",
+    <t>"pow":2.5,"flat":20,"elm":"fire","src":"int","range":5,"cd":6,"scope":"area","radius":3,"travel":{"type":"fall","img":"☄️","size":25,"deg":-135},"fx":{"img":"🔥"}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"lab":"流星雨",
 "des":"大範圍隕石轟炸，摧毀範圍內一切。"</t>
   </si>
   <si>
-    <t>"lab":"Meteor Shower",
+    <t xml:space="preserve">"lab":"Meteor Shower",
 "des":"大範圍隕石轟炸，摧毀範圍內一切。"</t>
   </si>
   <si>
-    <t>"scope":"group","radius":2,"pow":1.8,"flat":10,"elm":"fire","src":"int","cd":5,"travel":{"type":"spell","img":"🔥","size":25,"deg":-90},"fx":{}</t>
-  </si>
-  <si>
-    <t>"lab":"高級火球術",
-"des":"對自身周圍範圍內的敵人各自發射火球，造成範圍傷害。"</t>
-  </si>
-  <si>
-    <t>"lab":"Greater Fireball",
-"des":"Fires a fireball at each enemy within range around yourself."</t>
-  </si>
-  <si>
     <t>icebolt</t>
   </si>
   <si>
@@ -375,11 +385,11 @@
     <t>"pow":1.5,"flat":10,"elm":"ice","src":"int","range":5,"cd":3</t>
   </si>
   <si>
-    <t>"lab":"冰箭術",
+    <t xml:space="preserve">"lab":"冰箭術",
 "des":"單體冰錐。造成傷害並減速 30%。"</t>
   </si>
   <si>
-    <t>"lab":"Ice Bolt",
+    <t xml:space="preserve">"lab":"Ice Bolt",
 "des":"單體冰錐。造成傷害並減速 30%。"</t>
   </si>
   <si>
@@ -389,11 +399,11 @@
     <t>🧊</t>
   </si>
   <si>
-    <t>"lab":"冰牆術",
+    <t xml:space="preserve">"lab":"冰牆術",
 "des":"召喚可抵擋飛行道具的冰塊物理障礙物。"</t>
   </si>
   <si>
-    <t>"lab":"Ice Wall",
+    <t xml:space="preserve">"lab":"Ice Wall",
 "des":"召喚可抵擋飛行道具的冰塊物理障礙物。"</t>
   </si>
   <si>
@@ -403,18 +413,18 @@
     <t>🥶</t>
   </si>
   <si>
-    <t>"icebolt",
+    <t xml:space="preserve">"icebolt",
 "icewall"</t>
   </si>
   <si>
     <t>"pow":2.0,"flat":15,"elm":"ice","src":"int","range":5,"cd":4</t>
   </si>
   <si>
-    <t>"lab":"冰封術",
+    <t xml:space="preserve">"lab":"冰封術",
 "des":"將減速狀態轉為凍結，使敵方完全無法行動 3 秒。"</t>
   </si>
   <si>
-    <t>"lab":"Deep Freeze",
+    <t xml:space="preserve">"lab":"Deep Freeze",
 "des":"將減速狀態轉為凍結，使敵方完全無法行動 3 秒。"</t>
   </si>
   <si>
@@ -430,11 +440,11 @@
     <t>"pow":2.5,"flat":20,"elm":"ice","src":"int","range":5,"cd":6</t>
   </si>
   <si>
-    <t>"lab":"暴風雪",
+    <t xml:space="preserve">"lab":"暴風雪",
 "des":"大範圍持續性傷害，並有 10% 機率直接凍結敵人。"</t>
   </si>
   <si>
-    <t>"lab":"Blizzard",
+    <t xml:space="preserve">"lab":"Blizzard",
 "des":"大範圍持續性傷害，並有 10% 機率直接凍結敵人。"</t>
   </si>
   <si>
@@ -447,7 +457,7 @@
     <t>"pow":1.5,"flat":10,"elm":"poison","src":"int","range":5,"cd":3</t>
   </si>
   <si>
-    <t>"lab":"毒箭術",
+    <t xml:space="preserve">"lab":"毒箭術",
 "des":"遠程發射毒針，使目標進入每秒扣血的中毒狀態。"</t>
   </si>
   <si>
@@ -457,7 +467,7 @@
     <t>🌫️</t>
   </si>
   <si>
-    <t>"lab":"毒霧術",
+    <t xml:space="preserve">"lab":"毒霧術",
 "des":"在指定區域散佈致命毒氣。"</t>
   </si>
   <si>
@@ -467,14 +477,14 @@
     <t>🍄</t>
   </si>
   <si>
-    <t>"poisondart",
+    <t xml:space="preserve">"poisondart",
 "poisonmist"</t>
   </si>
   <si>
     <t>"pow":2.0,"flat":15,"elm":"poison","src":"int","range":5,"cd":4</t>
   </si>
   <si>
-    <t>"lab":"毒素引爆",
+    <t xml:space="preserve">"lab":"毒素引爆",
 "des":"使受毒者爆炸，將毒素噴濺至周圍目標。"</t>
   </si>
   <si>
@@ -487,11 +497,11 @@
     <t>"cd":2</t>
   </si>
   <si>
-    <t>"lab":"治療",
+    <t xml:space="preserve">"lab":"治療",
 "des":"恢復目標生命值。"</t>
   </si>
   <si>
-    <t>"lab":"Heal",
+    <t xml:space="preserve">"lab":"Heal",
 "des":"恢復目標生命值。"</t>
   </si>
   <si>
@@ -504,11 +514,11 @@
     <t>"cd":3</t>
   </si>
   <si>
-    <t>"lab":"解毒",
+    <t xml:space="preserve">"lab":"解毒",
 "des":"清除體內毒素。"</t>
   </si>
   <si>
-    <t>"lab":"Cure",
+    <t xml:space="preserve">"lab":"Cure",
 "des":"清除體內毒素。"</t>
   </si>
   <si>
@@ -518,11 +528,11 @@
     <t>☀️</t>
   </si>
   <si>
-    <t>"lab":"聖光",
+    <t xml:space="preserve">"lab":"聖光",
 "des":"移除 1 個負面狀態。"</t>
   </si>
   <si>
-    <t>"lab":"Holy Light",
+    <t xml:space="preserve">"lab":"Holy Light",
 "des":"移除 1 個負面狀態。"</t>
   </si>
   <si>
@@ -532,18 +542,18 @@
     <t>✨</t>
   </si>
   <si>
-    <t>"cure",
+    <t xml:space="preserve">"cure",
 "holylight"</t>
   </si>
   <si>
     <t>"cd":5</t>
   </si>
   <si>
-    <t>"lab":"淨化",
+    <t xml:space="preserve">"lab":"淨化",
 "des":"清除體內毒素，移除所有負面狀態。"</t>
   </si>
   <si>
-    <t>"lab":"Purify",
+    <t xml:space="preserve">"lab":"Purify",
 "des":"清除體內毒素，移除所有負面狀態。"</t>
   </si>
   <si>
@@ -553,11 +563,11 @@
     <t>💪</t>
   </si>
   <si>
-    <t>"lab":"力量增強",
+    <t xml:space="preserve">"lab":"力量增強",
 "des":"增加力量，可提升近戰傷害。"</t>
   </si>
   <si>
-    <t>"lab":"Strength Boost",
+    <t xml:space="preserve">"lab":"Strength Boost",
 "des":"增加力量，可提升近戰傷害。"</t>
   </si>
   <si>
@@ -567,11 +577,11 @@
     <t>👟</t>
   </si>
   <si>
-    <t>"lab":"敏捷增強",
+    <t xml:space="preserve">"lab":"敏捷增強",
 "des":"增加敏捷，可提升閃避。"</t>
   </si>
   <si>
-    <t>"lab":"Agility Boost",
+    <t xml:space="preserve">"lab":"Agility Boost",
 "des":"增加敏捷，可提升閃避。"</t>
   </si>
   <si>
@@ -581,52 +591,32 @@
     <t>🧠</t>
   </si>
   <si>
-    <t>"lab":"智力增強",
+    <t xml:space="preserve">"lab":"智力增強",
 "des":"增加智力，可提升法術效果。"</t>
   </si>
   <si>
-    <t>"lab":"Intelligence Boost",
+    <t xml:space="preserve">"lab":"Intelligence Boost",
 "des":"增加智力，可提升法術效果。"</t>
-  </si>
-  <si>
-    <t>fireballvolley</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>"fireball"</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>"fireballvolley",
-"firewall"</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="136"/>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="微軟正黑體 Light"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -659,7 +649,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -958,9 +948,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
@@ -970,11 +960,10 @@
     <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="64.140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="67.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1003,7 +992,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,7 +1013,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1044,7 +1033,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -1065,7 +1054,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="31.5" customHeight="1">
+    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -1082,7 +1071,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="31.5" customHeight="1">
+    <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
@@ -1100,25 +1089,25 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
     <col min="2" max="4" width="8.85546875" style="1" customWidth="1"/>
@@ -1126,11 +1115,10 @@
     <col min="6" max="6" width="14.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" style="1" customWidth="1"/>
     <col min="8" max="9" width="66.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1159,7 +1147,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
@@ -1182,7 +1170,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>38</v>
       </c>
@@ -1205,7 +1193,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>43</v>
       </c>
@@ -1231,7 +1219,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="31.5" customHeight="1">
+    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>49</v>
       </c>
@@ -1254,7 +1242,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="31.5" customHeight="1">
+    <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>55</v>
       </c>
@@ -1281,27 +1269,25 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
     <col min="2" max="5" width="8.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" style="1" customWidth="1"/>
     <col min="8" max="9" width="66.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1330,7 +1316,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>61</v>
       </c>
@@ -1353,7 +1339,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>66</v>
       </c>
@@ -1376,7 +1362,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>71</v>
       </c>
@@ -1403,16 +1389,15 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
@@ -1421,11 +1406,10 @@
     <col min="6" max="6" width="59.5703125" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1454,7 +1438,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>77</v>
       </c>
@@ -1478,7 +1462,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>82</v>
       </c>
@@ -1501,9 +1485,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>78</v>
@@ -1515,25 +1499,25 @@
         <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>167</v>
+        <v>88</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="31.5" customHeight="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
@@ -1542,24 +1526,24 @@
         <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>168</v>
+        <v>94</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="31.5" customHeight="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>33</v>
@@ -1568,38 +1552,38 @@
         <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
       <c r="F14" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
@@ -1608,11 +1592,10 @@
     <col min="6" max="6" width="14.140625" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1641,12 +1624,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -1655,22 +1638,22 @@
         <v>34</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -1679,21 +1662,21 @@
         <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1702,24 +1685,24 @@
         <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="31.5" customHeight="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
@@ -1728,42 +1711,42 @@
         <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
@@ -1773,11 +1756,10 @@
     <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="61" style="1" customWidth="1"/>
     <col min="9" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1806,12 +1788,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -1820,22 +1802,22 @@
         <v>34</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -1844,21 +1826,21 @@
         <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -1867,48 +1849,48 @@
         <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="16.5" customHeight="1">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
       <c r="F5" s="1"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
@@ -1918,11 +1900,10 @@
     <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="48.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="70" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1951,126 +1932,126 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="31.5" customHeight="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
       <c r="F13" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
@@ -2079,11 +2060,10 @@
     <col min="6" max="6" width="14.140625" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
     <col min="8" max="9" width="46" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2112,12 +2092,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+    <row r="2" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -2127,18 +2107,18 @@
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="31.5" customHeight="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>33</v>
@@ -2147,18 +2127,18 @@
         <v>51</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="31.5" customHeight="1">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>33</v>
@@ -2168,29 +2148,29 @@
       </c>
       <c r="E4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
       <c r="F12" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>